--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 13\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F1E369-C009-4C6D-BBE7-F451E92DC568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2030,6 +2030,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2214,78 +2274,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2370,8 +2358,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2402,6 +2388,20 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -25614,119 +25614,119 @@
     <cfRule type="duplicateValues" dxfId="97" priority="787"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D273:D298">
-    <cfRule type="duplicateValues" dxfId="96" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="217" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="216" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="94" priority="215" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="216" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="217" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D313:D323">
-    <cfRule type="duplicateValues" dxfId="91" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="210" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="211" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="212" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="212" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="211" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="210" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D324:D328 D330:D331">
-    <cfRule type="duplicateValues" dxfId="86" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="205" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="206" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="206" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="205" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D329">
     <cfRule type="duplicateValues" dxfId="81" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="240" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="241" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="242" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="240" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="241" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="242" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D332:D339">
     <cfRule type="duplicateValues" dxfId="76" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="200" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="200" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="199"/>
     <cfRule type="duplicateValues" dxfId="73" priority="201" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="72" priority="202" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D340">
     <cfRule type="duplicateValues" dxfId="71" priority="195" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="196" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="197" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="197" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="196" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D341:D346">
-    <cfRule type="duplicateValues" dxfId="68" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="223"/>
     <cfRule type="duplicateValues" dxfId="66" priority="225" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="65" priority="226" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="64" priority="227" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D364:D377">
-    <cfRule type="duplicateValues" dxfId="63" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="192" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="193" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="194" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="192" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="193" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="194" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D378:D379">
     <cfRule type="duplicateValues" dxfId="58" priority="277"/>
     <cfRule type="duplicateValues" dxfId="57" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="279" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="280" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="281" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="280" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="281" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="279" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D380">
-    <cfRule type="duplicateValues" dxfId="53" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="142" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="143" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="142" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="143" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D381:D387">
-    <cfRule type="duplicateValues" dxfId="45" priority="844"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="845"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="847"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="848"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="849"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="850" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="851" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="851" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="850" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D512:D582">
     <cfRule type="duplicateValues" dxfId="37" priority="819"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D583:D584">
-    <cfRule type="duplicateValues" dxfId="36" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="63" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="34" priority="62" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="63" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D585">
-    <cfRule type="duplicateValues" dxfId="31" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="59" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="28" priority="58" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="57" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D586">
-    <cfRule type="duplicateValues" dxfId="26" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="52" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="53" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="53" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D587">
-    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="39" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="39" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D588:D593">
     <cfRule type="duplicateValues" dxfId="13" priority="798"/>
@@ -25743,8 +25743,8 @@
     <cfRule type="duplicateValues" dxfId="4" priority="789" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="786" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="786" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
     <cfRule type="duplicateValues" dxfId="1" priority="783"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 15\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C8BA6A-52BD-4FF3-8879-12DF4C220F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1866,20 +1866,6 @@
   <dxfs count="178">
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1920,626 +1906,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2724,6 +2090,58 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2766,8 +2184,510 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3022,6 +2942,86 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -25446,262 +25446,262 @@
   <conditionalFormatting sqref="A353:A357 A89:A206 A208:A348">
     <cfRule type="duplicateValues" dxfId="175" priority="963"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A486:A517">
+    <cfRule type="duplicateValues" dxfId="174" priority="1031"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A486:A524">
+    <cfRule type="duplicateValues" dxfId="173" priority="1033"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A527">
-    <cfRule type="duplicateValues" dxfId="174" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A528:A554">
-    <cfRule type="duplicateValues" dxfId="173" priority="956"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="956"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A555:A556">
+    <cfRule type="duplicateValues" dxfId="169" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="171" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117">
-    <cfRule type="duplicateValues" dxfId="170" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="309" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="310" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="311" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="309" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="310" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="311" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D118:D134 D109:D111 D94:D106 D114:D116">
-    <cfRule type="duplicateValues" dxfId="165" priority="1007"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="1008" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="1009"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="1010" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="1008" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="1007"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="1010" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="1009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D124:D130">
-    <cfRule type="duplicateValues" dxfId="161" priority="1027" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="1027" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D166">
-    <cfRule type="duplicateValues" dxfId="160" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="294" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="157" priority="295" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="156" priority="296" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="294" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="292"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:D169 D135:D137 D160:D165">
-    <cfRule type="duplicateValues" dxfId="155" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="908" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="908" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:D169">
-    <cfRule type="duplicateValues" dxfId="153" priority="913"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="914" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="914" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D170:D195">
-    <cfRule type="duplicateValues" dxfId="151" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="276" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="148" priority="277" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="278" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="276" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="278" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D209:D211">
-    <cfRule type="duplicateValues" dxfId="146" priority="1002"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="1003"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="1004" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="1005" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="1006" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="1006" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="1005" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="1004" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="1002"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D212:D216 D218:D219">
-    <cfRule type="duplicateValues" dxfId="141" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="256" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="257" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="254"/>
     <cfRule type="duplicateValues" dxfId="137" priority="258" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="257" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D217">
-    <cfRule type="duplicateValues" dxfId="136" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="314" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="315" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="316" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="314" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="315" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="316" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D220:D227">
-    <cfRule type="duplicateValues" dxfId="131" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="251" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="252" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="253" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="253" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="252" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="251" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D228">
-    <cfRule type="duplicateValues" dxfId="126" priority="246" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="247" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="248" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="248" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="247" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="246" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D229:D234">
-    <cfRule type="duplicateValues" dxfId="123" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="299" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="300" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="301" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="299" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="300" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="301" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D252:D263">
-    <cfRule type="duplicateValues" dxfId="118" priority="926"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="927"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="928" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="929" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="930" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="926"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="928" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="929" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="930" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D264:D269">
-    <cfRule type="duplicateValues" dxfId="113" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="903"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D277:D280">
-    <cfRule type="duplicateValues" dxfId="112" priority="921"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="922"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="923" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="924" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="925" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="923" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="924" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="925" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D281:D285">
-    <cfRule type="duplicateValues" dxfId="107" priority="997"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="998"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="999" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="1000" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="1001" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="1001" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="1000" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="999" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D287">
-    <cfRule type="duplicateValues" dxfId="102" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="324" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="325" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="326" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="324" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="325" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="326" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D288:D293">
-    <cfRule type="duplicateValues" dxfId="97" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="213" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="94" priority="214" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="93" priority="215" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="213" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D294:D299">
-    <cfRule type="duplicateValues" dxfId="92" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="208" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="209" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="207"/>
     <cfRule type="duplicateValues" dxfId="88" priority="210" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="209" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="208" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="206"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D300:D312">
+    <cfRule type="duplicateValues" dxfId="84" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="1039" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1040" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="1041" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D313:D314">
-    <cfRule type="duplicateValues" dxfId="87" priority="352" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="352" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D321:D325">
-    <cfRule type="duplicateValues" dxfId="83" priority="356" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="356" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="358"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D326:D331">
-    <cfRule type="duplicateValues" dxfId="79" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="363"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="365"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="366" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="367" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="366" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="367" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D332:D343">
-    <cfRule type="duplicateValues" dxfId="71" priority="373"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="376"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="377"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="379" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="380" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="380" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="379" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D344">
-    <cfRule type="duplicateValues" dxfId="63" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="167" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="168" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="168" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="167" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D346:D348">
-    <cfRule type="duplicateValues" dxfId="55" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="975"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="976"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="979"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="980" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="981" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="981" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="979"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="980" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D349:D352">
-    <cfRule type="duplicateValues" dxfId="47" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="986"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="987"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="989"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="990" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="991" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="991" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="990" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="987"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D353:D357">
-    <cfRule type="duplicateValues" dxfId="39" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="142" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="143" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="142" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="143" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D555">
+    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D556">
+    <cfRule type="duplicateValues" dxfId="18" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D557:D561">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="31" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="1029" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1029" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="29" priority="879"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="880" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="880" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="879"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="27" priority="877"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="878" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A517">
-    <cfRule type="duplicateValues" dxfId="25" priority="1031"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A486:A524">
-    <cfRule type="duplicateValues" dxfId="24" priority="1033"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D300:D312">
-    <cfRule type="duplicateValues" dxfId="23" priority="1037"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="1038"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1039" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1040" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1041" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A555:A556">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D555">
-    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="17" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="18" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D556">
-    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="11" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="12" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="13" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D557:D561">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="878" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="877"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 16\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750B23A2-C511-49A3-8926-E43252CE3605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1607,8 +1607,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1619,8 +1617,16 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1785,16 +1791,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1817,8 +1815,46 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2123,96 +2159,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2297,6 +2245,58 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -24319,174 +24319,174 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A338:A340">
+    <cfRule type="duplicateValues" dxfId="114" priority="1798"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A346 A234:A258 A273:A305 A261:A271 A307:A344">
+    <cfRule type="duplicateValues" dxfId="113" priority="1747"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A544:A545">
+    <cfRule type="duplicateValues" dxfId="112" priority="1737"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A550:A553">
+    <cfRule type="duplicateValues" dxfId="111" priority="1711"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A558">
-    <cfRule type="duplicateValues" dxfId="114" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="113" priority="1430"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="1430"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D234:D258">
-    <cfRule type="duplicateValues" dxfId="112" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="232" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="233" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="108" priority="234" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="233" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="232" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D274:D284">
-    <cfRule type="duplicateValues" dxfId="107" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="227" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="228" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="229" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="228" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="227" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="229" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D285:D289 D291:D292">
-    <cfRule type="duplicateValues" dxfId="102" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="222" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="223" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="224" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="222" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="223" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="224" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D290">
-    <cfRule type="duplicateValues" dxfId="97" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="257" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="258" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="93" priority="259" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="258" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="257" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="256"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D293:D300">
-    <cfRule type="duplicateValues" dxfId="92" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="217" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="218" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="88" priority="219" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="218" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="217" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D301">
-    <cfRule type="duplicateValues" dxfId="87" priority="212" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="213" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="214" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="213" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="212" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="214" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D302:D307">
-    <cfRule type="duplicateValues" dxfId="84" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="242" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="243" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="244" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="242" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="243" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="244" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D325:D336">
-    <cfRule type="duplicateValues" dxfId="79" priority="1662"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="1663"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="1664" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="1665" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="75" priority="1666" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1665" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1664" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1663"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D337">
-    <cfRule type="duplicateValues" dxfId="74" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="159" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="158"/>
     <cfRule type="duplicateValues" dxfId="67" priority="160" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="159" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D338 D341:D344">
+    <cfRule type="duplicateValues" dxfId="62" priority="1797" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1790"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1791"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1792"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1793"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1794"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1795"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1796" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D544">
-    <cfRule type="duplicateValues" dxfId="66" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="104" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="105" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="105" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="104" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D545">
-    <cfRule type="duplicateValues" dxfId="61" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="99" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="100" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="100" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D546:D549">
+    <cfRule type="duplicateValues" dxfId="44" priority="1728" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1727" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1726"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1724"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1723"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1721"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1725"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D550:D551">
-    <cfRule type="duplicateValues" dxfId="56" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="57" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="58" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="58" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D552">
-    <cfRule type="duplicateValues" dxfId="51" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="52" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="53" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="53" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="52" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D553">
-    <cfRule type="duplicateValues" dxfId="46" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="39" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="40" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D557">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="5" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="6" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="6" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D558 D554:D556">
+    <cfRule type="duplicateValues" dxfId="13" priority="1683" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1684" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1681"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1680"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1677"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1682"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1679"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1678"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="33" priority="1675"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="1676" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1675"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1676" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="31" priority="1428"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="1429" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1429" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="29" priority="1426"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1427" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D558 D554:D556">
-    <cfRule type="duplicateValues" dxfId="27" priority="1677"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="1678"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="1679"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="1680"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="1681"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="1682"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1683" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1684" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A550:A553">
-    <cfRule type="duplicateValues" dxfId="19" priority="1711"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D546:D549">
-    <cfRule type="duplicateValues" dxfId="18" priority="1721"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1722"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1723"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1724"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1725"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="1726"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1727" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1728" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A544:A545">
-    <cfRule type="duplicateValues" dxfId="10" priority="1737"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A346 A234:A258 A273:A305 A261:A271 A307:A344">
-    <cfRule type="duplicateValues" dxfId="9" priority="1747"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D338 D341:D344">
-    <cfRule type="duplicateValues" dxfId="8" priority="1790"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1791"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1792"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1793"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1794"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1795"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1796" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1797" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A338:A340">
-    <cfRule type="duplicateValues" dxfId="0" priority="1798"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1427" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 17\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A32D7B-BBB1-4920-89AE-AB7F98A4B507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1860,6 +1860,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -1964,6 +2014,20 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2034,70 +2098,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -23290,123 +23290,123 @@
   </sheetData>
   <autoFilter ref="A1:L543" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A327:A329">
+    <cfRule type="duplicateValues" dxfId="73" priority="1662"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A335 A223:A260 A262:A333">
+    <cfRule type="duplicateValues" dxfId="72" priority="1631"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A455:A509">
+    <cfRule type="duplicateValues" dxfId="71" priority="1628"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A455:A515">
+    <cfRule type="duplicateValues" dxfId="70" priority="1629"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A520">
-    <cfRule type="duplicateValues" dxfId="73" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A521">
+    <cfRule type="duplicateValues" dxfId="68" priority="1604"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A522">
-    <cfRule type="duplicateValues" dxfId="72" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A523:A527">
+    <cfRule type="duplicateValues" dxfId="62" priority="1601"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="69" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D223:D248">
-    <cfRule type="duplicateValues" dxfId="68" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="239" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="240" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="241" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="240" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="241" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="239" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D263:D273">
-    <cfRule type="duplicateValues" dxfId="63" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="234" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="235" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="236" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="234" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="235" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="236" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D274:D278 D280:D281">
-    <cfRule type="duplicateValues" dxfId="58" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="229" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="230" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="231" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="229" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="230" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="231" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D279">
-    <cfRule type="duplicateValues" dxfId="53" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="264" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="265" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="266" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="266" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="265" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="264" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="263"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D282:D289">
-    <cfRule type="duplicateValues" dxfId="48" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="224" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="225" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="224" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="225" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D290">
-    <cfRule type="duplicateValues" dxfId="43" priority="219" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="220" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="221" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="221" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="220" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="219" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D291:D296">
-    <cfRule type="duplicateValues" dxfId="40" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="249" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="250" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="251" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="251" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="250" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="249" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D314:D325">
-    <cfRule type="duplicateValues" dxfId="35" priority="1590"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="1591"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="1592" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="1593" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="1594" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1593" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1594" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1590"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1591"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1592" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D326">
-    <cfRule type="duplicateValues" dxfId="30" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="166" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="167" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="167" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="166" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D327 D330:D333">
+    <cfRule type="duplicateValues" dxfId="13" priority="1654"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1655"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1656"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1658"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1659"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1660" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1661" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="22" priority="1595"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1596" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1596" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="20" priority="1225"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1226" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1223"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1224" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A523:A527">
-    <cfRule type="duplicateValues" dxfId="16" priority="1600"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1601"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A521">
-    <cfRule type="duplicateValues" dxfId="14" priority="1602"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="1603"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1604"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A455:A509">
-    <cfRule type="duplicateValues" dxfId="11" priority="1628"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A455:A515">
-    <cfRule type="duplicateValues" dxfId="10" priority="1629"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A335 A223:A260 A262:A333">
-    <cfRule type="duplicateValues" dxfId="9" priority="1631"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D327 D330:D333">
-    <cfRule type="duplicateValues" dxfId="8" priority="1654"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1655"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1656"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1657"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1658"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1659"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1660" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1661" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A327:A329">
-    <cfRule type="duplicateValues" dxfId="0" priority="1662"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1224" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 18\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD3A33-8E7A-4EE0-AD3B-53B7771E375D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1583,40 +1583,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1771,6 +1737,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1781,48 +1749,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2025,6 +1951,80 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -13426,91 +13426,91 @@
   </sheetData>
   <autoFilter ref="A1:L538" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A448:A449">
+    <cfRule type="duplicateValues" dxfId="57" priority="1597"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A455:A462">
+    <cfRule type="duplicateValues" dxfId="56" priority="1587"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="57" priority="1340"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D448">
-    <cfRule type="duplicateValues" dxfId="56" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="105" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="104"/>
     <cfRule type="duplicateValues" dxfId="52" priority="107" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D449">
-    <cfRule type="duplicateValues" dxfId="51" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="100" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="101" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="102" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="100" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="102" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D450:D454">
+    <cfRule type="duplicateValues" dxfId="44" priority="1596" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1595" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1594"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1590"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1593"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1592"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1591"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1589"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D455:D456">
-    <cfRule type="duplicateValues" dxfId="46" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="54" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="55" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="56" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="55" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="56" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459">
-    <cfRule type="duplicateValues" dxfId="41" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="49" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="50" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D460">
-    <cfRule type="duplicateValues" dxfId="36" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="44" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="45" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="45" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D462">
-    <cfRule type="duplicateValues" dxfId="31" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="31" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D463:D465">
+    <cfRule type="duplicateValues" dxfId="13" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1571"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1572"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1576" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1577" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="23" priority="1551"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="1552" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1551"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1552" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="21" priority="1338"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1339" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1338"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1339" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="19" priority="1336"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1337" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D463:D465">
-    <cfRule type="duplicateValues" dxfId="17" priority="1570"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1571"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1572"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1573"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="1574"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1575"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1576" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1577" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A455:A462">
-    <cfRule type="duplicateValues" dxfId="9" priority="1587"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D450:D454">
-    <cfRule type="duplicateValues" dxfId="8" priority="1589"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1590"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1591"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1592"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1593"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1594"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1595" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1596" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A448:A449">
-    <cfRule type="duplicateValues" dxfId="0" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1336"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1337" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 20\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A702EC9-9055-4B43-A090-63E9B5E61B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1591,8 +1591,48 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1635,130 +1675,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2003,6 +1919,90 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -13144,90 +13144,90 @@
   </sheetData>
   <autoFilter ref="A1:L410" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A212:A329">
+    <cfRule type="duplicateValues" dxfId="54" priority="1819"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A316:A318">
+    <cfRule type="duplicateValues" dxfId="53" priority="1816"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A399:A401">
+    <cfRule type="duplicateValues" dxfId="52" priority="1809"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A404:A409">
+    <cfRule type="duplicateValues" dxfId="51" priority="1799"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="54" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D399:D400">
-    <cfRule type="duplicateValues" dxfId="53" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="95" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="96" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="95" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="96" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D402:D403">
+    <cfRule type="duplicateValues" dxfId="44" priority="1805"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1808" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1807" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1806"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1803"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1802"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1801"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D404">
-    <cfRule type="duplicateValues" dxfId="48" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="54" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="55" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="56" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="54" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="55" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="56" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D406">
-    <cfRule type="duplicateValues" dxfId="43" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="49" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="50" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D407">
-    <cfRule type="duplicateValues" dxfId="38" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="44" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="45" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="45" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D409">
-    <cfRule type="duplicateValues" dxfId="33" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="31" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="32" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="31" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D410">
-    <cfRule type="duplicateValues" dxfId="25" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="23" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="17" priority="1688"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1689" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1689" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="15" priority="1475"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1476" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1476" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1473"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1474" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A404:A409">
-    <cfRule type="duplicateValues" dxfId="11" priority="1799"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D402:D403">
-    <cfRule type="duplicateValues" dxfId="10" priority="1801"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1802"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1803"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1804"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1805"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1806"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1807" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1808" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A399:A401">
-    <cfRule type="duplicateValues" dxfId="2" priority="1809"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A316:A318">
-    <cfRule type="duplicateValues" dxfId="1" priority="1816"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A212:A329">
-    <cfRule type="duplicateValues" dxfId="0" priority="1819"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1474" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 21\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{311F3C4E-9349-4C3F-8DE1-4AE7C2242754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 23\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F373F78-5980-4B62-B49C-92684D93C635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -9814,23 +9814,23 @@
   </sheetData>
   <autoFilter ref="A1:L422" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A147:A151">
+    <cfRule type="duplicateValues" dxfId="7" priority="2088"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1873"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1873"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="6" priority="2084"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2085" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2084"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2085" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1871"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1872" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1871"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1872" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="2" priority="1869"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1870" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A147:A151">
-    <cfRule type="duplicateValues" dxfId="0" priority="2088"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1869"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1870" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A300A-F30A-4675-852E-13C100151B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F9A106-E0CF-480A-BE5F-9A65B9F02CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$417</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="309">
   <si>
     <t>SKU</t>
   </si>
@@ -921,9 +921,6 @@
     <t>Pipeline</t>
   </si>
   <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>Open Order</t>
   </si>
   <si>
@@ -931,17 +928,49 @@
   </si>
   <si>
     <t>Dispatch Partner</t>
+  </si>
+  <si>
+    <t>V-03</t>
+  </si>
+  <si>
+    <t>SC-01</t>
+  </si>
+  <si>
+    <t>GS-02</t>
+  </si>
+  <si>
+    <t>SC-05</t>
+  </si>
+  <si>
+    <t>DH-01</t>
+  </si>
+  <si>
+    <t>CAP-05</t>
+  </si>
+  <si>
+    <t>CFM-01</t>
+  </si>
+  <si>
+    <t>SC-04</t>
+  </si>
+  <si>
+    <t>MR-01</t>
+  </si>
+  <si>
+    <t>HSB-04</t>
+  </si>
+  <si>
+    <t>BR-01</t>
+  </si>
+  <si>
+    <t>PB-01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1000,12 +1029,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1056,13 +1079,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1091,20 +1113,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
@@ -1590,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L430"/>
+  <dimension ref="A1:L431"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -10088,1472 +10104,1446 @@
       </c>
     </row>
     <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C369" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I369" s="11">
-        <v>1472</v>
+      <c r="A369" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B369" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I369" s="10">
+        <v>68</v>
       </c>
       <c r="J369" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K369" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K369" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L369" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B370" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C370" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I370" s="11">
-        <v>2000</v>
+      <c r="A370" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B370" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I370" s="10">
+        <v>13</v>
       </c>
       <c r="J370" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K370" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K370" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L370" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B371" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I371" s="11">
-        <v>2000</v>
+      <c r="A371" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B371" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I371" s="10">
+        <v>39</v>
       </c>
       <c r="J371" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K371" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K371" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L371" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B372" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C372" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I372" s="11">
-        <v>2000</v>
+      <c r="A372" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B372" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I372" s="10">
+        <v>48</v>
       </c>
       <c r="J372" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K372" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K372" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L372" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B373" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I373" s="11">
-        <v>996</v>
+      <c r="A373" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B373" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I373" s="10">
+        <v>29</v>
       </c>
       <c r="J373" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K373" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K373" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L373" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B374" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I374" s="11">
-        <v>405</v>
+      <c r="A374" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B374" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I374" s="10">
+        <v>11</v>
       </c>
       <c r="J374" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K374" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K374" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L374" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B375" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C375" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I375" s="11">
-        <v>504</v>
+      <c r="A375" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B375" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I375" s="10">
+        <v>57</v>
       </c>
       <c r="J375" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K375" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K375" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L375" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B376" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C376" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I376" s="11">
-        <v>200</v>
+      <c r="A376" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B376" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I376" s="10">
+        <v>35</v>
       </c>
       <c r="J376" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K376" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K376" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L376" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B377" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C377" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I377" s="11">
-        <v>2000</v>
+      <c r="A377" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B377" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I377" s="10">
+        <v>3</v>
       </c>
       <c r="J377" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K377" s="10" t="s">
-        <v>294</v>
+      <c r="K377" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L377" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B378" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C378" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I378" s="11">
-        <v>2000</v>
+      <c r="A378" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B378" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I378" s="10">
+        <v>36</v>
       </c>
       <c r="J378" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K378" s="10" t="s">
-        <v>294</v>
+      <c r="K378" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L378" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B379" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C379" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I379" s="12">
-        <v>1000</v>
+      <c r="A379" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B379" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I379" s="10">
+        <v>3</v>
       </c>
       <c r="J379" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K379" s="10" t="s">
-        <v>294</v>
+      <c r="K379" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L379" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B380" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C380" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I380" s="11">
-        <v>1000</v>
+      <c r="A380" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B380" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I380" s="10">
+        <v>24</v>
       </c>
       <c r="J380" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K380" s="10" t="s">
-        <v>294</v>
+      <c r="K380" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L380" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B381" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C381" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I381" s="12">
-        <v>1002</v>
+      <c r="A381" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B381" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I381" s="10">
+        <v>12</v>
       </c>
       <c r="J381" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K381" s="10" t="s">
+      <c r="K381" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L381" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B382" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I382" s="10">
+        <v>8</v>
+      </c>
+      <c r="J382" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K382" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L382" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B383" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I383" s="10">
+        <v>26</v>
+      </c>
+      <c r="J383" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K383" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L383" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B384" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I384" s="10">
+        <v>7</v>
+      </c>
+      <c r="J384" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K384" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L384" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B385" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I385" s="10">
+        <v>13</v>
+      </c>
+      <c r="J385" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K385" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L385" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B386" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I386" s="10">
+        <v>3</v>
+      </c>
+      <c r="J386" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K386" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L386" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B387" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I387" s="10">
+        <v>88</v>
+      </c>
+      <c r="J387" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K387" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L387" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B388" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I388" s="10">
+        <v>26</v>
+      </c>
+      <c r="J388" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K388" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L388" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B389" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I389" s="10">
+        <v>82</v>
+      </c>
+      <c r="J389" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K389" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L389" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B390" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I390" s="10">
+        <v>6</v>
+      </c>
+      <c r="J390" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K390" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L390" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B391" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I391" s="10">
+        <v>7</v>
+      </c>
+      <c r="J391" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K391" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L391" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B392" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I392" s="10">
+        <v>15</v>
+      </c>
+      <c r="J392" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K392" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L392" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B393" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I393" s="10">
+        <v>41</v>
+      </c>
+      <c r="J393" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K393" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L393" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B394" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I394" s="10">
+        <v>5</v>
+      </c>
+      <c r="J394" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K394" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L394" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B395" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I395" s="10">
+        <v>25</v>
+      </c>
+      <c r="J395" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K395" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L395" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B396" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I396" s="10">
+        <v>9</v>
+      </c>
+      <c r="J396" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K396" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L396" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B397" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I397" s="10">
+        <v>13</v>
+      </c>
+      <c r="J397" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K397" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L397" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B398" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I398" s="10">
+        <v>9</v>
+      </c>
+      <c r="J398" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K398" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L398" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B399" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I399" s="10">
+        <v>47</v>
+      </c>
+      <c r="J399" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K399" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L399" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B400" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I400" s="10">
+        <v>16</v>
+      </c>
+      <c r="J400" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K400" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L400" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B401" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I401" s="10">
+        <v>6</v>
+      </c>
+      <c r="J401" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K401" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L401" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B402" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I402" s="10">
+        <v>6</v>
+      </c>
+      <c r="J402" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K402" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L402" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B403" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I403" s="10">
+        <v>10</v>
+      </c>
+      <c r="J403" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K403" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L403" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B404" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I404" s="10">
+        <v>94</v>
+      </c>
+      <c r="J404" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K404" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L404" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B405" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I405" s="10">
+        <v>127</v>
+      </c>
+      <c r="J405" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K405" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L405" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B406" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I406" s="10">
+        <v>15</v>
+      </c>
+      <c r="J406" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K406" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L406" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B407" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I407" s="10">
+        <v>10</v>
+      </c>
+      <c r="J407" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K407" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L407" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A408" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B408" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I408" s="10">
+        <v>20</v>
+      </c>
+      <c r="J408" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K408" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L408" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I409" s="10">
+        <v>16</v>
+      </c>
+      <c r="J409" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K409" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L409" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B410" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I410" s="10">
+        <v>10</v>
+      </c>
+      <c r="J410" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K410" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L410" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A411" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B411" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I411" s="10">
+        <v>8</v>
+      </c>
+      <c r="J411" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K411" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L411" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A412" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B412" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I412" s="10">
+        <v>62</v>
+      </c>
+      <c r="J412" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K412" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L412" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A413" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B413" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I413" s="10">
+        <v>37</v>
+      </c>
+      <c r="J413" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K413" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L413" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B414" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I414" s="10">
+        <v>30</v>
+      </c>
+      <c r="J414" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K414" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L414" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B415" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I415" s="10">
+        <v>50</v>
+      </c>
+      <c r="J415" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K415" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L415" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A416" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B416" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I416" s="10">
+        <v>9</v>
+      </c>
+      <c r="J416" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K416" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L416" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B417" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I417" s="10">
+        <v>21</v>
+      </c>
+      <c r="J417" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K417" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L417" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I418" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J418" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I419" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A420" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I420" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I421" s="1">
+        <v>996</v>
+      </c>
+      <c r="J421" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I422" s="1">
+        <v>405</v>
+      </c>
+      <c r="J422" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A423" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I423" s="1">
+        <v>200</v>
+      </c>
+      <c r="J423" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A424" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I424" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J424" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="L381" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B382" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I382" s="13">
-        <v>68</v>
-      </c>
-      <c r="J382" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K382" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L382" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="13" t="s">
+    </row>
+    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A425" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I425" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J425" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I426" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J426" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B383" s="13" t="s">
+      <c r="B427" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C383" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I383" s="13">
-        <v>13</v>
-      </c>
-      <c r="J383" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K383" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L383" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B384" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C384" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I384" s="13">
-        <v>39</v>
-      </c>
-      <c r="J384" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K384" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L384" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B385" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C385" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I385" s="13">
-        <v>48</v>
-      </c>
-      <c r="J385" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K385" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L385" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B386" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C386" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I386" s="13">
-        <v>29</v>
-      </c>
-      <c r="J386" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K386" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B387" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I387" s="13">
-        <v>11</v>
-      </c>
-      <c r="J387" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K387" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L387" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B388" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C388" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I388" s="13">
-        <v>57</v>
-      </c>
-      <c r="J388" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K388" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L388" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B389" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I389" s="13">
-        <v>35</v>
-      </c>
-      <c r="J389" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K389" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L389" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B390" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C390" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I390" s="13">
-        <v>3</v>
-      </c>
-      <c r="J390" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K390" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L390" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B391" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C391" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I391" s="13">
-        <v>36</v>
-      </c>
-      <c r="J391" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K391" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L391" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B392" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I392" s="13">
-        <v>3</v>
-      </c>
-      <c r="J392" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K392" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L392" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B393" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C393" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I393" s="13">
-        <v>24</v>
-      </c>
-      <c r="J393" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K393" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L393" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B394" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I394" s="13">
-        <v>12</v>
-      </c>
-      <c r="J394" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K394" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L394" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B395" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C395" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I395" s="13">
-        <v>8</v>
-      </c>
-      <c r="J395" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K395" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L395" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B396" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I396" s="13">
-        <v>26</v>
-      </c>
-      <c r="J396" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K396" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L396" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B397" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I397" s="13">
-        <v>7</v>
-      </c>
-      <c r="J397" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K397" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L397" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B398" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I398" s="13">
-        <v>13</v>
-      </c>
-      <c r="J398" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K398" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L398" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B399" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C399" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I399" s="13">
-        <v>3</v>
-      </c>
-      <c r="J399" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K399" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L399" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B400" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C400" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I400" s="13">
-        <v>88</v>
-      </c>
-      <c r="J400" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K400" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L400" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B401" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C401" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I401" s="13">
-        <v>26</v>
-      </c>
-      <c r="J401" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K401" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L401" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B402" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I402" s="13">
-        <v>82</v>
-      </c>
-      <c r="J402" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K402" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L402" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B403" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I403" s="13">
-        <v>6</v>
-      </c>
-      <c r="J403" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K403" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L403" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B404" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C404" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I404" s="13">
-        <v>7</v>
-      </c>
-      <c r="J404" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K404" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L404" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B405" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C405" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I405" s="13">
-        <v>15</v>
-      </c>
-      <c r="J405" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K405" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L405" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B406" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C406" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I406" s="13">
-        <v>41</v>
-      </c>
-      <c r="J406" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K406" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L406" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B407" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I407" s="13">
-        <v>5</v>
-      </c>
-      <c r="J407" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K407" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L407" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B408" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I408" s="13">
-        <v>25</v>
-      </c>
-      <c r="J408" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K408" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L408" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="13" t="s">
+      <c r="C427" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I427" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J427" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A428" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B409" s="13" t="s">
+      <c r="B428" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C409" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I409" s="13">
-        <v>9</v>
-      </c>
-      <c r="J409" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K409" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L409" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B410" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="C410" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I410" s="13">
-        <v>13</v>
-      </c>
-      <c r="J410" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K410" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L410" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B411" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I411" s="13">
-        <v>9</v>
-      </c>
-      <c r="J411" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K411" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="13" t="s">
+      <c r="C428" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I428" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J428" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B412" s="13" t="s">
+      <c r="B429" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C412" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I412" s="13">
-        <v>47</v>
-      </c>
-      <c r="J412" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K412" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L412" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B413" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C413" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I413" s="13">
-        <v>16</v>
-      </c>
-      <c r="J413" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K413" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L413" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B414" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I414" s="13">
-        <v>6</v>
-      </c>
-      <c r="J414" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K414" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L414" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="B415" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I415" s="13">
-        <v>6</v>
-      </c>
-      <c r="J415" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K415" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L415" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="13" t="s">
+      <c r="C429" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I429" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J429" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A430" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B416" s="13" t="s">
+      <c r="B430" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I416" s="13">
-        <v>10</v>
-      </c>
-      <c r="J416" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K416" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L416" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B417" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C417" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I417" s="13">
-        <v>94</v>
-      </c>
-      <c r="J417" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K417" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L417" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B418" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I418" s="13">
-        <v>127</v>
-      </c>
-      <c r="J418" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K418" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L418" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B419" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I419" s="13">
-        <v>15</v>
-      </c>
-      <c r="J419" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K419" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L419" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B420" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I420" s="13">
-        <v>10</v>
-      </c>
-      <c r="J420" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K420" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L420" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B421" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C421" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I421" s="13">
-        <v>20</v>
-      </c>
-      <c r="J421" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K421" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L421" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B422" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I422" s="13">
-        <v>16</v>
-      </c>
-      <c r="J422" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K422" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L422" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B423" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I423" s="13">
-        <v>10</v>
-      </c>
-      <c r="J423" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K423" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L423" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B424" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I424" s="13">
-        <v>8</v>
-      </c>
-      <c r="J424" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K424" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L424" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B425" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I425" s="13">
-        <v>62</v>
-      </c>
-      <c r="J425" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K425" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L425" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B426" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I426" s="13">
-        <v>37</v>
-      </c>
-      <c r="J426" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K426" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L426" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B427" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I427" s="13">
-        <v>30</v>
-      </c>
-      <c r="J427" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K427" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L427" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B428" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I428" s="13">
-        <v>50</v>
-      </c>
-      <c r="J428" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K428" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L428" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="13" t="s">
+      <c r="C430" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I430" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J430" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A431" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B429" s="13" t="s">
+      <c r="B431" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C429" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I429" s="13">
-        <v>9</v>
-      </c>
-      <c r="J429" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K429" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L429" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B430" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I430" s="13">
-        <v>21</v>
-      </c>
-      <c r="J430" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K430" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L430" s="1" t="s">
-        <v>244</v>
+      <c r="C431" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I431" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J431" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L430" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A430">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  <conditionalFormatting sqref="A155:A264">
+    <cfRule type="duplicateValues" dxfId="14" priority="2198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A251:A253">
+    <cfRule type="duplicateValues" dxfId="13" priority="2195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A265">
+    <cfRule type="duplicateValues" dxfId="12" priority="2189"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A369:A413">
+    <cfRule type="duplicateValues" dxfId="9" priority="2182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A369:A416">
+    <cfRule type="duplicateValues" dxfId="8" priority="2180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A417">
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="12" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A382:A429">
-    <cfRule type="duplicateValues" dxfId="6" priority="2180"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A382:A426">
-    <cfRule type="duplicateValues" dxfId="5" priority="2182"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A377:A381">
-    <cfRule type="duplicateValues" dxfId="4" priority="2185"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A369:A373">
-    <cfRule type="duplicateValues" dxfId="3" priority="2188"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A265">
-    <cfRule type="duplicateValues" dxfId="2" priority="2189"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A251:A253">
-    <cfRule type="duplicateValues" dxfId="1" priority="2195"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A155:A264">
-    <cfRule type="duplicateValues" dxfId="0" priority="2198"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -9148,7 +9148,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 29\Nexlev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 30\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9180C48B-6377-46BA-AF5E-2C63E0B79A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C742A376-10EE-4AD8-BE6C-83B6CA83C76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="371">
   <si>
     <t>SKU</t>
   </si>
@@ -150,6 +150,9 @@
     <t>FBA79273</t>
   </si>
   <si>
+    <t>FBA79277</t>
+  </si>
+  <si>
     <t>FBA79278</t>
   </si>
   <si>
@@ -427,6 +430,9 @@
   </si>
   <si>
     <t>B0D2LKB4BJ</t>
+  </si>
+  <si>
+    <t>B0D672NXC8</t>
   </si>
   <si>
     <t>B0D86ZC9YT</t>
@@ -910,6 +916,9 @@
   </si>
   <si>
     <t>SC-04</t>
+  </si>
+  <si>
+    <t>SC-03</t>
   </si>
   <si>
     <t>SC-02</t>
@@ -1357,7 +1366,7 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="92">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1990,6 +1999,140 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2498,7 +2641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L263"/>
+  <dimension ref="A1:L268"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2556,382 +2699,382 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I2" s="3">
         <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I4" s="3">
         <v>7</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I6" s="3">
         <v>13</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I7" s="3">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I8" s="3">
         <v>2</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I9" s="3">
         <v>4</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I10" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I11" s="3">
         <v>32</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I12" s="3">
         <v>29</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I13" s="3">
         <v>2</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I14" s="3">
         <v>51</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I15" s="3">
         <v>43</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I17" s="3">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I18" s="3">
         <v>314</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I19" s="3">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I20" s="3">
         <v>550</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1">
@@ -2939,119 +3082,119 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I21" s="3">
-        <v>1045</v>
+        <v>1088</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I22" s="3">
-        <v>1825</v>
+        <v>1814</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I23" s="3">
         <v>614</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I24" s="3">
-        <v>29</v>
+        <v>417</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I25" s="3">
-        <v>344</v>
+        <v>25</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>157</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I26" s="3">
-        <v>25</v>
+        <v>826</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1">
@@ -3059,59 +3202,59 @@
         <v>63</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I27" s="3">
-        <v>852</v>
+        <v>244</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I28" s="3">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I29" s="3">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1">
@@ -3119,19 +3262,19 @@
         <v>60</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I30" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1">
@@ -3139,199 +3282,199 @@
         <v>59</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I31" s="3">
-        <v>31</v>
+        <v>664</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I32" s="3">
-        <v>672</v>
+        <v>2</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I33" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I34" s="3">
-        <v>7</v>
+        <v>699</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I35" s="3">
-        <v>777</v>
+        <v>400</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I36" s="3">
-        <v>400</v>
+        <v>91</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>89</v>
+        <v>224</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I37" s="3">
-        <v>91</v>
+        <v>363</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>222</v>
+        <v>14</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I38" s="3">
-        <v>363</v>
+        <v>113</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I39" s="3">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I40" s="3">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1">
@@ -3339,39 +3482,39 @@
         <v>31</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I41" s="3">
         <v>49</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I42" s="3">
         <v>43</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1">
@@ -3379,19 +3522,19 @@
         <v>29</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I43" s="3">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1">
@@ -3399,19 +3542,19 @@
         <v>28</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I44" s="3">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1">
@@ -3419,119 +3562,119 @@
         <v>27</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I45" s="3">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I46" s="3">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I47" s="3">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I48" s="3">
-        <v>586</v>
+        <v>123</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I49" s="3">
-        <v>34</v>
+        <v>586</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>226</v>
+        <v>39</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I50" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1">
@@ -3542,1016 +3685,1016 @@
         <v>229</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I51" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>56</v>
+        <v>230</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>434</v>
+        <v>9</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I53" s="3">
-        <v>55</v>
+        <v>443</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I54" s="3">
-        <v>1046</v>
+        <v>55</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>230</v>
+        <v>17</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I55" s="3">
-        <v>187</v>
+        <v>1046</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I56" s="3">
-        <v>33</v>
+        <v>187</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I57" s="3">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I58" s="3">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>232</v>
+        <v>67</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I59" s="3">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>49</v>
+        <v>234</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>117</v>
+        <v>235</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I60" s="3">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I61" s="3">
-        <v>1560</v>
+        <v>25</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>310</v>
       </c>
       <c r="I62" s="3">
-        <v>564</v>
+        <v>1548</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I63" s="3">
-        <v>934</v>
+        <v>35</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1">
       <c r="A64" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I64" s="3">
-        <v>60</v>
+        <v>564</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I65" s="3">
-        <v>39</v>
+        <v>928</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I66" s="3">
-        <v>1668</v>
+        <v>36</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>234</v>
+        <v>30</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I67" s="3">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I68" s="3">
-        <v>1411</v>
+        <v>1600</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>318</v>
       </c>
       <c r="I69" s="3">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1">
       <c r="A70" s="4" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>319</v>
       </c>
       <c r="I70" s="3">
-        <v>1034</v>
+        <v>1339</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>236</v>
+        <v>109</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I71" s="3">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>322</v>
       </c>
       <c r="I72" s="3">
-        <v>486</v>
+        <v>994</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>165</v>
+        <v>238</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>323</v>
       </c>
       <c r="I73" s="3">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1">
       <c r="A74" s="4" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I74" s="3">
-        <v>262</v>
+        <v>466</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I75" s="3">
-        <v>1316</v>
+        <v>12</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1">
       <c r="A76" s="4" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I76" s="3">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I77" s="3">
-        <v>25</v>
+        <v>1319</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I78" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I79" s="3">
-        <v>774</v>
+        <v>47</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>237</v>
+        <v>74</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I80" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I81" s="3">
-        <v>17</v>
+        <v>771</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I82" s="3">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I83" s="3">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I84" s="3">
-        <v>432</v>
+        <v>287</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="15" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I85" s="3">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I86" s="3">
-        <v>165</v>
+        <v>446</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I87" s="3">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I88" s="3">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15" customHeight="1">
       <c r="A90" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>341</v>
       </c>
       <c r="I90" s="3">
-        <v>579</v>
+        <v>34</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" customHeight="1">
       <c r="A91" s="4" t="s">
-        <v>88</v>
+        <v>241</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>179</v>
+        <v>242</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>342</v>
       </c>
       <c r="I91" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15" customHeight="1">
       <c r="A92" s="4" t="s">
-        <v>241</v>
+        <v>88</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3">
-        <v>66</v>
+        <v>573</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" customHeight="1">
       <c r="A93" s="4" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I93" s="3">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" customHeight="1">
       <c r="A94" s="4" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I94" s="3">
-        <v>1147</v>
+        <v>66</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1">
       <c r="A95" s="4" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I95" s="3">
-        <v>1010</v>
+        <v>4</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1">
       <c r="A96" s="4" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I96" s="3">
-        <v>2504</v>
+        <v>1147</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15" customHeight="1">
       <c r="A97" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>349</v>
       </c>
       <c r="I97" s="3">
-        <v>665</v>
+        <v>1010</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" customHeight="1">
       <c r="A98" s="4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>350</v>
       </c>
       <c r="I98" s="3">
-        <v>1637</v>
+        <v>2504</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" customHeight="1">
       <c r="A99" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>185</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I99" s="3">
-        <v>2767</v>
+        <v>683</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15" customHeight="1">
       <c r="A100" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>186</v>
+        <v>93</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I100" s="3">
-        <v>11</v>
+        <v>1627</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15" customHeight="1">
       <c r="A101" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>189</v>
+        <v>96</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I101" s="3">
-        <v>1</v>
+        <v>2721</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15" customHeight="1">
@@ -4559,419 +4702,419 @@
         <v>97</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I102" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="15" customHeight="1">
       <c r="A103" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I103" s="3">
-        <v>377</v>
+        <v>1</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1">
       <c r="A104" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I104" s="3">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="15" customHeight="1">
       <c r="A105" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D105" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="I105" s="3">
         <v>357</v>
       </c>
-      <c r="I105" s="3">
-        <v>2</v>
-      </c>
       <c r="J105" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="15" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I106" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="15" customHeight="1">
       <c r="A107" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="I107" s="3">
+        <v>2</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="15" customHeight="1">
+      <c r="A108" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B108" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C108" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I108" s="3">
+        <v>12</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="15" customHeight="1">
+      <c r="A109" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D107" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="I107" s="3">
-        <v>320</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="15" customHeight="1">
-      <c r="A108" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B108" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="I108" s="12">
-        <v>1</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="15" customHeight="1">
-      <c r="A109" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B109" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C109" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="I109" s="12">
-        <v>70</v>
+      <c r="C109" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="I109" s="3">
+        <v>212</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="15" customHeight="1">
       <c r="A110" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="I110" s="12">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="15" customHeight="1">
       <c r="A111" s="15" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>231</v>
+        <v>130</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="I111" s="12">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="15" customHeight="1">
       <c r="A112" s="15" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>252</v>
+        <v>363</v>
       </c>
       <c r="I112" s="12">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="15" customHeight="1">
       <c r="A113" s="15" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D113" s="13" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="I113" s="12">
         <v>48</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="15" customHeight="1">
       <c r="A114" s="15" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="I114" s="12">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="15" customHeight="1">
       <c r="A115" s="15" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="I115" s="12">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>66</v>
+        <v>224</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="I116" s="12">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="15" customHeight="1">
       <c r="A117" s="15" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="I117" s="12">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B118" s="13" t="s">
         <v>160</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="I118" s="12">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="15" customHeight="1">
       <c r="A119" s="15" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="I119" s="12">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="15" customHeight="1">
       <c r="A120" s="15" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>351</v>
+        <v>270</v>
       </c>
       <c r="I120" s="12">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="15" customHeight="1">
       <c r="A121" s="15" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="I121" s="12">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="15" customHeight="1">
       <c r="A122" s="15" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="I122" s="12">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="15" customHeight="1">
@@ -4979,2867 +5122,2984 @@
         <v>70</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I123" s="12">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="15" customHeight="1">
       <c r="A124" s="15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I124" s="12">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="15" customHeight="1">
       <c r="A125" s="15" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>337</v>
+        <v>265</v>
       </c>
       <c r="I125" s="12">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="15" customHeight="1">
       <c r="A126" s="15" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="I126" s="12">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="15" customHeight="1">
       <c r="A127" s="15" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="I127" s="12">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="15" customHeight="1">
       <c r="A128" s="15" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>274</v>
+        <v>352</v>
       </c>
       <c r="I128" s="12">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="15" customHeight="1">
       <c r="A129" s="15" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="I129" s="12">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="15" customHeight="1">
       <c r="A130" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I130" s="12">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="15" customHeight="1">
       <c r="A131" s="15" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="I131" s="12">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="15" customHeight="1">
       <c r="A132" s="15" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I132" s="12">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="15" customHeight="1">
       <c r="A133" s="15" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="I133" s="12">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="15" customHeight="1">
       <c r="A134" s="15" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="I134" s="12">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="15" customHeight="1">
       <c r="A135" s="15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="I135" s="12">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="15" customHeight="1">
       <c r="A136" s="15" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="I136" s="12">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="15" customHeight="1">
       <c r="A137" s="15" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="I137" s="12">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="15" customHeight="1">
       <c r="A138" s="15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="I138" s="12">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="15" customHeight="1">
       <c r="A139" s="15" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="I139" s="12">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="15" customHeight="1">
       <c r="A140" s="15" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="I140" s="12">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="15" customHeight="1">
       <c r="A141" s="15" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="I141" s="12">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="15" customHeight="1">
       <c r="A142" s="15" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="I142" s="12">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="15" customHeight="1">
       <c r="A143" s="15" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="I143" s="12">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="15" customHeight="1">
       <c r="A144" s="15" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="I144" s="12">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="15" customHeight="1">
       <c r="A145" s="15" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="I145" s="12">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="15" customHeight="1">
       <c r="A146" s="15" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="I146" s="12">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="15" customHeight="1">
       <c r="A147" s="15" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="I147" s="12">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="15" customHeight="1">
       <c r="A148" s="15" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="I148" s="12">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="15" customHeight="1">
       <c r="A149" s="15" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="I149" s="12">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="15" customHeight="1">
       <c r="A150" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="I150" s="12">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="15" customHeight="1">
       <c r="A151" s="15" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="I151" s="12">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="15" customHeight="1">
       <c r="A152" s="15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="I152" s="12">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="15" customHeight="1">
       <c r="A153" s="15" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="I153" s="12">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="15" customHeight="1">
       <c r="A154" s="15" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="I154" s="12">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="15" customHeight="1">
       <c r="A155" s="15" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="I155" s="12">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="15" customHeight="1">
       <c r="A156" s="15" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="I156" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="15" customHeight="1">
       <c r="A157" s="15" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I157" s="12">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="15" customHeight="1">
       <c r="A158" s="15" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I158" s="12">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="15" customHeight="1">
       <c r="A159" s="15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C159" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="I159" s="12">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="15" customHeight="1">
       <c r="A160" s="15" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="I160" s="12">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="15" customHeight="1">
       <c r="A161" s="15" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D161" s="13" t="s">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="I161" s="12">
         <v>20</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="15" customHeight="1">
       <c r="A162" s="15" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="C162" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="I162" s="12">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="15" customHeight="1">
       <c r="A163" s="15" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D163" s="13" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I163" s="12">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="15" customHeight="1">
       <c r="A164" s="15" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D164" s="13" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
       <c r="I164" s="12">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="15" customHeight="1">
       <c r="A165" s="15" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="C165" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D165" s="13" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="I165" s="12">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="15" customHeight="1">
       <c r="A166" s="15" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="I166" s="12">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="15" customHeight="1">
       <c r="A167" s="15" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="C167" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="I167" s="12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="15" customHeight="1">
       <c r="A168" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>334</v>
+        <v>259</v>
       </c>
       <c r="I168" s="12">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="15" customHeight="1">
       <c r="A169" s="15" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="I169" s="12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="15" customHeight="1">
       <c r="A170" s="15" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="I170" s="12">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="15" customHeight="1">
       <c r="A171" s="15" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D171" s="13" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="I171" s="12">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="15" customHeight="1">
       <c r="A172" s="15" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="I172" s="12">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="15" customHeight="1">
       <c r="A173" s="15" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="I173" s="12">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="15" customHeight="1">
       <c r="A174" s="15" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="I174" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="15" customHeight="1">
       <c r="A175" s="15" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="I175" s="12">
         <v>5</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="15" customHeight="1">
       <c r="A176" s="15" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="I176" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="15" customHeight="1">
       <c r="A177" s="15" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C177" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="I177" s="12">
+        <v>5</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="15" customHeight="1">
+      <c r="A178" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C178" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="I178" s="12">
+        <v>5</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="15" customHeight="1">
+      <c r="A179" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C179" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D179" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="I179" s="12">
         <v>7</v>
       </c>
-      <c r="J177" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="15" customHeight="1">
-      <c r="A178" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="I178" s="3">
-        <v>111</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="15" customHeight="1">
-      <c r="A179" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="I179" s="3">
-        <v>110</v>
-      </c>
       <c r="J179" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="I180" s="3">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="15" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="I181" s="3">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="15" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="I182" s="3">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="15" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>237</v>
+        <v>88</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="I183" s="3">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="15" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="I184" s="3">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="15" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>47</v>
+        <v>239</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="I185" s="3">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="15" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>337</v>
+        <v>271</v>
       </c>
       <c r="I186" s="3">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="15" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="I187" s="3">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="188" spans="1:10" ht="15" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="I188" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="15" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="I189" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="I190" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="15" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="I191" s="3">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="15" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="I192" s="3">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="15" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="I193" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="15" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="I194" s="3">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="15" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="I195" s="3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="15" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I196" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="15" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="I197" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="15" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="I198" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="15" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="I199" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="15" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="I200" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="15" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="I201" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="15" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="I202" s="3">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="15" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="I203" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="15" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="I204" s="3">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="15" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="I205" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="15" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>351</v>
+        <v>276</v>
       </c>
       <c r="I206" s="3">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="207" spans="1:10" ht="15" customHeight="1">
-      <c r="A207" s="16" t="s">
-        <v>37</v>
+      <c r="A207" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="I207" s="13">
-        <v>121</v>
+        <v>274</v>
+      </c>
+      <c r="I207" s="3">
+        <v>6</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="15" customHeight="1">
-      <c r="A208" s="13" t="s">
-        <v>61</v>
+      <c r="A208" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="I208" s="13">
-        <v>76</v>
+        <v>354</v>
+      </c>
+      <c r="I208" s="3">
+        <v>24</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="15" customHeight="1">
-      <c r="A209" s="13" t="s">
-        <v>57</v>
+      <c r="A209" s="16" t="s">
+        <v>38</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="I209" s="13">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="210" spans="1:10" ht="15" customHeight="1">
       <c r="A210" s="13" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="I210" s="13">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="211" spans="1:10" ht="15" customHeight="1">
       <c r="A211" s="13" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="I211" s="13">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="15" customHeight="1">
       <c r="A212" s="13" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>350</v>
+        <v>292</v>
       </c>
       <c r="I212" s="13">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="15" customHeight="1">
       <c r="A213" s="13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="I213" s="13">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="15" customHeight="1">
       <c r="A214" s="13" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="I214" s="13">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="15" customHeight="1">
       <c r="A215" s="13" t="s">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="I215" s="13">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="15" customHeight="1">
       <c r="A216" s="13" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="I216" s="13">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="15" customHeight="1">
       <c r="A217" s="13" t="s">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="I217" s="13">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="15" customHeight="1">
       <c r="A218" s="13" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="I218" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="15" customHeight="1">
       <c r="A219" s="13" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="I219" s="13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="15" customHeight="1">
       <c r="A220" s="13" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="I220" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="15" customHeight="1">
       <c r="A221" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I221" s="13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="15" customHeight="1">
       <c r="A222" s="13" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="I222" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="15" customHeight="1">
       <c r="A223" s="13" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="I223" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="15" customHeight="1">
-      <c r="A224" s="16" t="s">
-        <v>23</v>
+      <c r="A224" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="I224" s="13">
         <v>12</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="225" spans="1:10" ht="15" customHeight="1">
       <c r="A225" s="13" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="I225" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="226" spans="1:10" ht="15" customHeight="1">
-      <c r="A226" s="13" t="s">
-        <v>94</v>
+      <c r="A226" s="16" t="s">
+        <v>23</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="I226" s="13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="15" customHeight="1">
       <c r="A227" s="13" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="I227" s="13">
         <v>9</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="15" customHeight="1">
       <c r="A228" s="13" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="I228" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="15" customHeight="1">
       <c r="A229" s="13" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="I229" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="15" customHeight="1">
       <c r="A230" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="I230" s="13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="15" customHeight="1">
       <c r="A231" s="13" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="I231" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="15" customHeight="1">
       <c r="A232" s="13" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="I232" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="15" customHeight="1">
       <c r="A233" s="13" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>231</v>
+        <v>134</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I233" s="13">
         <v>6</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="15" customHeight="1">
       <c r="A234" s="13" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
       <c r="I234" s="13">
         <v>6</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="15" customHeight="1">
       <c r="A235" s="13" t="s">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>340</v>
+        <v>304</v>
       </c>
       <c r="I235" s="13">
         <v>6</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="15" customHeight="1">
       <c r="A236" s="13" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="I236" s="13">
         <v>6</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="15" customHeight="1">
       <c r="A237" s="13" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="I237" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="15" customHeight="1">
       <c r="A238" s="13" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I238" s="13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="239" spans="1:10" ht="15" customHeight="1">
       <c r="A239" s="13" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="I239" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="240" spans="1:10" ht="15" customHeight="1">
       <c r="A240" s="13" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="I240" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="241" spans="1:10" ht="15" customHeight="1">
       <c r="A241" s="13" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I241" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="242" spans="1:10" ht="15" customHeight="1">
       <c r="A242" s="13" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="I242" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="243" spans="1:10" ht="15" customHeight="1">
       <c r="A243" s="13" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="I243" s="13">
+        <v>2</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="15" customHeight="1">
+      <c r="A244" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I244" s="13">
         <v>1</v>
       </c>
-      <c r="J243" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="15" customHeight="1">
-      <c r="A244" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B244" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D244" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I244" s="8">
-        <v>2000</v>
-      </c>
-      <c r="J244" s="7" t="s">
-        <v>200</v>
+      <c r="J244" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="15" customHeight="1">
-      <c r="A245" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D245" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="I245" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J245" s="7" t="s">
-        <v>200</v>
+      <c r="A245" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I245" s="13">
+        <v>1</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="246" spans="1:10" ht="15" customHeight="1">
       <c r="A246" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D246" s="14" t="s">
-        <v>340</v>
+        <v>253</v>
       </c>
       <c r="I246" s="8">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="J246" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="247" spans="1:10" ht="15" customHeight="1">
-      <c r="A247" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>189</v>
+      <c r="A247" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D247" s="9" t="s">
-        <v>353</v>
+        <v>200</v>
+      </c>
+      <c r="D247" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="I247" s="8">
-        <v>252</v>
+        <v>1052</v>
       </c>
       <c r="J247" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="248" spans="1:10" ht="15" customHeight="1">
       <c r="A248" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="I248" s="8">
-        <v>2000</v>
+        <v>1002</v>
       </c>
       <c r="J248" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="249" spans="1:10" ht="15" customHeight="1">
       <c r="A249" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="I249" s="8">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="J249" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="250" spans="1:10" ht="15" customHeight="1">
       <c r="A250" s="4" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="I250" s="8">
-        <v>2004</v>
+        <v>250</v>
       </c>
       <c r="J250" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="251" spans="1:10" ht="15" customHeight="1">
       <c r="A251" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="I251" s="10">
-        <v>2002</v>
+        <v>347</v>
+      </c>
+      <c r="I251" s="8">
+        <v>1002</v>
       </c>
       <c r="J251" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="15" customHeight="1">
+      <c r="A252" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C252" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" ht="15" customHeight="1">
-      <c r="A252" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B252" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D252" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="I252" s="10">
-        <v>1000</v>
+      <c r="D252" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="I252" s="8">
+        <v>252</v>
       </c>
       <c r="J252" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="253" spans="1:10" ht="15" customHeight="1">
       <c r="A253" s="4" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D253" s="14" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="I253" s="8">
-        <v>1020</v>
+        <v>2000</v>
       </c>
       <c r="J253" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="254" spans="1:10" ht="15" customHeight="1">
       <c r="A254" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="I254" s="8">
-        <v>800</v>
+        <v>1948</v>
       </c>
       <c r="J254" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="15" customHeight="1">
       <c r="A255" s="4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="I255" s="10">
-        <v>4506</v>
+        <v>294</v>
+      </c>
+      <c r="I255" s="8">
+        <v>2004</v>
       </c>
       <c r="J255" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="15" customHeight="1">
       <c r="A256" s="4" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>184</v>
+        <v>105</v>
       </c>
       <c r="C256" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D256" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="I256" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J256" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="15" customHeight="1">
+      <c r="A257" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D257" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="I257" s="10">
+        <v>1000</v>
+      </c>
+      <c r="J257" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="15" customHeight="1">
+      <c r="A258" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D258" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="I258" s="8">
+        <v>1020</v>
+      </c>
+      <c r="J258" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="15" customHeight="1">
+      <c r="A259" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D259" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="I259" s="8">
+        <v>800</v>
+      </c>
+      <c r="J259" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="15" customHeight="1">
+      <c r="A260" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D260" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="I260" s="10">
+        <v>3504</v>
+      </c>
+      <c r="J260" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="15" customHeight="1">
+      <c r="A261" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D261" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="I261" s="8">
+        <v>2000</v>
+      </c>
+      <c r="J261" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="15" customHeight="1">
+      <c r="A262" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="I262" s="8">
+        <v>207</v>
+      </c>
+      <c r="J262" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="15" customHeight="1">
+      <c r="A263" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="I263" s="8">
+        <v>2000</v>
+      </c>
+      <c r="J263" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="15" customHeight="1">
+      <c r="A264" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B264" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D256" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="I256" s="8">
-        <v>2000</v>
-      </c>
-      <c r="J256" s="7" t="s">
+      <c r="C264" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" ht="15" customHeight="1">
-      <c r="A257" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D257" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="I257" s="8">
-        <v>207</v>
-      </c>
-      <c r="J257" s="7" t="s">
+      <c r="D264" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="I264" s="8">
+        <v>1500</v>
+      </c>
+      <c r="J264" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="15" customHeight="1">
+      <c r="A265" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C265" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" ht="15" customHeight="1">
-      <c r="A258" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D258" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="I258" s="8">
-        <v>2000</v>
-      </c>
-      <c r="J258" s="7" t="s">
+      <c r="D265" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="I265" s="8">
+        <v>200</v>
+      </c>
+      <c r="J265" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="15" customHeight="1">
+      <c r="A266" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B266" s="3"/>
+      <c r="C266" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" ht="15" customHeight="1">
-      <c r="A259" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D259" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="I259" s="8">
-        <v>1500</v>
-      </c>
-      <c r="J259" s="7" t="s">
+      <c r="D266" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="I266" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J266" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="15" customHeight="1">
+      <c r="A267" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B267" s="18"/>
+      <c r="C267" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" ht="15" customHeight="1">
-      <c r="A260" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D260" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="I260" s="8">
-        <v>200</v>
-      </c>
-      <c r="J260" s="7" t="s">
+      <c r="D267" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="I267" s="8">
+        <v>500</v>
+      </c>
+      <c r="J267" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="15" customHeight="1">
+      <c r="A268" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="B268" s="18"/>
+      <c r="C268" s="5" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" ht="15" customHeight="1">
-      <c r="A261" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="B261" s="3"/>
-      <c r="C261" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D261" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="I261" s="8">
+      <c r="D268" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="I268" s="8">
         <v>1000</v>
       </c>
-      <c r="J261" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" ht="15" customHeight="1">
-      <c r="A262" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B262" s="18"/>
-      <c r="C262" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D262" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="I262" s="8">
-        <v>500</v>
-      </c>
-      <c r="J262" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" ht="15" customHeight="1">
-      <c r="A263" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="B263" s="18"/>
-      <c r="C263" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D263" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="I263" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J263" s="7" t="s">
-        <v>201</v>
+      <c r="J268" s="7" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L263" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L268" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="78" priority="2241"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D244">
-    <cfRule type="duplicateValues" dxfId="77" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="77" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="78" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="79" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="2365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D246">
-    <cfRule type="duplicateValues" dxfId="72" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="72" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="73" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="74" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="94" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="95" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="96" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D247">
-    <cfRule type="duplicateValues" dxfId="67" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="68" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="69" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D247:D248">
+    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="89" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="90" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="91" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D249:D251">
+  <conditionalFormatting sqref="D250">
+    <cfRule type="duplicateValues" dxfId="80" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="85" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="86" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D251">
+    <cfRule type="duplicateValues" dxfId="75" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="72" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="73" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D252">
+    <cfRule type="duplicateValues" dxfId="67" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="65" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D254:D256">
     <cfRule type="duplicateValues" dxfId="59" priority="35"/>
     <cfRule type="duplicateValues" dxfId="58" priority="36"/>
     <cfRule type="duplicateValues" dxfId="57" priority="37" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="56" priority="38" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="55" priority="39" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D252">
+  <conditionalFormatting sqref="D257">
     <cfRule type="duplicateValues" dxfId="54" priority="30"/>
     <cfRule type="duplicateValues" dxfId="53" priority="31"/>
     <cfRule type="duplicateValues" dxfId="52" priority="32" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="51" priority="33" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="50" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D254">
+  <conditionalFormatting sqref="D259">
     <cfRule type="duplicateValues" dxfId="49" priority="25"/>
     <cfRule type="duplicateValues" dxfId="48" priority="26"/>
     <cfRule type="duplicateValues" dxfId="47" priority="27" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="46" priority="28" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="45" priority="29" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D255">
+  <conditionalFormatting sqref="D260">
     <cfRule type="duplicateValues" dxfId="44" priority="17"/>
     <cfRule type="duplicateValues" dxfId="43" priority="18"/>
     <cfRule type="duplicateValues" dxfId="42" priority="19"/>
@@ -7850,65 +8110,65 @@
     <cfRule type="duplicateValues" dxfId="37" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="36" priority="2452"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="2453" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2576"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="2577" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="34" priority="2239"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="2240" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="2364" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="32" priority="2237"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="2238" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2362" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D256">
-    <cfRule type="duplicateValues" dxfId="30" priority="2536"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="2537"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="2538"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="2539"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="2540"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="2541"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2542" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2543" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D261">
+    <cfRule type="duplicateValues" dxfId="30" priority="2655"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2656"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2657"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="2658"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2659"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2660"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2661" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2662" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D257:D263">
-    <cfRule type="duplicateValues" dxfId="22" priority="2544"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2545"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2546"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="2547"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2548"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2549"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2550" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2551" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D262:D268">
+    <cfRule type="duplicateValues" dxfId="22" priority="2663"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2664"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2665"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2666"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2667"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2668"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2669" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2670" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A248:A256">
-    <cfRule type="duplicateValues" dxfId="14" priority="2561"/>
+  <conditionalFormatting sqref="A253:A261">
+    <cfRule type="duplicateValues" dxfId="14" priority="2680"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A244:A246">
-    <cfRule type="duplicateValues" dxfId="13" priority="2562"/>
+  <conditionalFormatting sqref="A246:A251">
+    <cfRule type="duplicateValues" dxfId="13" priority="2682"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A207:A243">
-    <cfRule type="duplicateValues" dxfId="12" priority="2573"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2574"/>
+  <conditionalFormatting sqref="A209:A245">
+    <cfRule type="duplicateValues" dxfId="12" priority="2693"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2694"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="10" priority="2583"/>
+  <conditionalFormatting sqref="A109">
+    <cfRule type="duplicateValues" dxfId="10" priority="2703"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D107">
-    <cfRule type="duplicateValues" dxfId="9" priority="2584"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2585"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2586"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2587"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2588"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2589"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2590" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2591" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D109">
+    <cfRule type="duplicateValues" dxfId="9" priority="2704"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2705"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2706"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2707"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2708"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2709"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2710" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2711" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A94:A96">
-    <cfRule type="duplicateValues" dxfId="1" priority="2597"/>
+  <conditionalFormatting sqref="A96:A98">
+    <cfRule type="duplicateValues" dxfId="1" priority="2717"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A106">
-    <cfRule type="duplicateValues" dxfId="0" priority="2600"/>
+  <conditionalFormatting sqref="A2:A108">
+    <cfRule type="duplicateValues" dxfId="0" priority="2720"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L266"/>
+  <dimension ref="A1:L260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>1176</v>
+        <v>888</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>602</v>
+        <v>482</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79475</t>
+          <t>FBA79467</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0DJFJZMC6</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TIC-04</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1489,12 +1489,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79475</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DJFJZMC6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>TIC-04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1525,12 +1525,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79474</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>TIC-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>653</v>
+        <v>16</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>653</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1597,12 +1597,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SW-01</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1633,12 +1633,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SW-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>415</v>
+        <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1669,12 +1669,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79589</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>394</v>
+        <v>67</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1705,12 +1705,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79698</t>
+          <t>FBA79589</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0D9KCKY9F</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SS-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1741,12 +1741,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA79468</t>
+          <t>FBA79698</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0DCK7J87D</t>
+          <t>B0D9KCKY9F</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SPM-01</t>
+          <t>SS-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA79468</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DCK7J87D</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>SPM-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>93</v>
+        <v>353</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79277</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1849,12 +1849,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79262</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0CYSMBCB8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1885,12 +1885,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA78998</t>
+          <t>FBA79277</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0CDQ5NBH8</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NP-05</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1921,12 +1921,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA78996</t>
+          <t>FBA79262</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0CDQ6G4TC</t>
+          <t>B0CYSMBCB8</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NP-03</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>603</v>
+        <v>48</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1957,12 +1957,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA78998</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0CDQ5NBH8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>NP-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>558</v>
+        <v>43</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA78994</t>
+          <t>FBA78996</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0CDQ98FDM</t>
+          <t>B0CDQ6G4TC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NP-01</t>
+          <t>NP-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>359</v>
+        <v>603</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2029,12 +2029,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>40</v>
+        <v>558</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2065,12 +2065,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79596</t>
+          <t>FBA78994</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0CDQ98FDM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MG-01</t>
+          <t>NP-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>124</v>
+        <v>358</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2101,12 +2101,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>586</v>
+        <v>40</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2137,12 +2137,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79572</t>
+          <t>FBA79596</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0DKJVWM8Q</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LE-07</t>
+          <t>MG-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2173,12 +2173,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79569</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0DKJRML4K</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LE-06</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>506</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>443</v>
+        <v>73</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2245,12 +2245,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79443</t>
+          <t>FBA79572</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DKJVWM8Q</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LE-03</t>
+          <t>LE-07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2281,12 +2281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79569</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DKJRML4K</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>LE-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>1046</v>
+        <v>9</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>187</v>
+        <v>443</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79591</t>
+          <t>FBA79443</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0DM66B2DW</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>LE-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2389,12 +2389,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>996</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2425,12 +2425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>33</v>
+        <v>187</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2461,12 +2461,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA79571</t>
+          <t>FBA79591</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0DKK12XWR</t>
+          <t>B0DM66B2DW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>IPL-01</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2497,12 +2497,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2533,12 +2533,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>1433</v>
+        <v>33</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2569,12 +2569,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79571</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DKK12XWR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>IPL-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>550</v>
+        <v>22</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2641,12 +2641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>924</v>
+        <v>1433</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79333</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D63DTKQB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>1490</v>
+        <v>543</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA78979</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0CDPQXPC1</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GS-01</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>9</v>
+        <v>924</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>1254</v>
+        <v>4</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2857,12 +2857,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>875</v>
+        <v>1348</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2929,12 +2929,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79375</t>
+          <t>FBA78979</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0CSG3FC4G</t>
+          <t>B0CDPQXPC1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ET-03-BL</t>
+          <t>GS-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>458</v>
+        <v>994</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>157</v>
+        <v>805</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3073,12 +3073,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79375</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0CSG3FC4G</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>ET-03-BL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>1320</v>
+        <v>39</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>31</v>
+        <v>458</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>771</v>
+        <v>1080</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3253,12 +3253,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79266</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0D2LGR3GG</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79273</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>HS-02</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>285</v>
+        <v>10</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3361,12 +3361,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>113</v>
+        <v>771</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3397,12 +3397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79266</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D2LGR3GG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>452</v>
+        <v>9</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3433,12 +3433,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>203</v>
+        <v>282</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79265</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>34</v>
+        <v>452</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3577,12 +3577,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79684</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0DVC9Q219</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AP-02</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3613,12 +3613,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>537</v>
+        <v>122</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79693</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0DVC91Q7J</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3721,22 +3721,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79003</t>
+          <t>FBA79684</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0CFH6C6YM</t>
+          <t>B0DVC9Q219</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TR-05</t>
+          <t>AP-02</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3757,22 +3757,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3793,22 +3793,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>1146</v>
+        <v>377</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3829,22 +3829,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79693</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DVC91Q7J</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>1005</v>
+        <v>41</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79003</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0CFH6C6YM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>TR-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>2503</v>
+        <v>65</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>578</v>
+        <v>2</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>1599</v>
+        <v>1146</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3973,12 +3973,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>2698</v>
+        <v>955</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4009,12 +4009,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79849</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CFM-03</t>
+          <t>ETC-07</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>11</v>
+        <v>2503</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4045,12 +4045,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>578</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79988</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AP-04</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>479</v>
+        <v>1593</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4117,12 +4117,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79989</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CAP-05</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>356</v>
+        <v>2693</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4153,12 +4153,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79992</t>
+          <t>FBA79849</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>CFM-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4225,12 +4225,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79988</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>AP-04</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>399</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4261,12 +4261,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79984</t>
+          <t>FBA79989</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>CAP-05</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4297,22 +4297,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4320,11 +4320,11 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -4333,22 +4333,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79273</t>
+          <t>FBA79993</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>HS-02</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -4356,11 +4356,11 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -4369,22 +4369,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4392,11 +4392,11 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -4405,22 +4405,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4428,11 +4428,11 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -4441,12 +4441,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79598</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BM-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4464,11 +4464,11 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -4477,12 +4477,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4500,11 +4500,11 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -4513,12 +4513,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79468</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0DCK7J87D</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SPM-01</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4536,11 +4536,11 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -4549,12 +4549,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4572,11 +4572,11 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -4585,12 +4585,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4608,11 +4608,11 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -4621,22 +4621,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4644,11 +4644,11 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -4657,12 +4657,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79492</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>V-02</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4680,11 +4680,11 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -4693,22 +4693,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4716,11 +4716,11 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -4729,22 +4729,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79599</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DRD8J8R5</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>VC-06</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -4752,11 +4752,11 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -4765,12 +4765,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4788,11 +4788,11 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -4801,12 +4801,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4824,11 +4824,11 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -4837,12 +4837,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79565</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0DKJZDY72</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VC-04</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4860,11 +4860,11 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -4873,12 +4873,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4896,11 +4896,11 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -4909,12 +4909,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79474</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>TIC-03</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4932,11 +4932,11 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -4945,22 +4945,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4968,11 +4968,11 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>195</v>
+        <v>14</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -4981,12 +4981,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79381</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ETR-06</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5004,11 +5004,11 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -5017,12 +5017,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79467</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5040,11 +5040,11 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -5053,12 +5053,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5076,11 +5076,11 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -5089,12 +5089,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5112,11 +5112,11 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -5125,12 +5125,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5148,11 +5148,11 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -5161,22 +5161,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5184,11 +5184,11 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>179</v>
+        <v>9</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -5197,12 +5197,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5220,11 +5220,11 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -5256,11 +5256,11 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -5269,12 +5269,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5292,11 +5292,11 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -5305,12 +5305,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5328,11 +5328,11 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -5341,12 +5341,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5364,11 +5364,11 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -5377,12 +5377,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5400,11 +5400,11 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -5413,22 +5413,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79693</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DVC91Q7J</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -5436,11 +5436,11 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -5449,12 +5449,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5472,11 +5472,11 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -5485,12 +5485,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5508,11 +5508,11 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -5521,12 +5521,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5544,11 +5544,11 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -5557,12 +5557,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79381</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>ETR-06</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5580,11 +5580,11 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -5593,12 +5593,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA78996</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0CDQ6G4TC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>NP-03</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5616,11 +5616,11 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>166</v>
+        <v>3</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -5629,12 +5629,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5652,11 +5652,11 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -5665,12 +5665,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5688,11 +5688,11 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -5701,22 +5701,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -5724,11 +5724,11 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -5737,12 +5737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -5760,11 +5760,11 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -5773,12 +5773,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -5796,11 +5796,11 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -5809,12 +5809,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -5832,11 +5832,11 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -5845,12 +5845,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79589</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -5868,11 +5868,11 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -5881,12 +5881,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -5904,11 +5904,11 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -5917,12 +5917,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA79598</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>BM-02</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -5940,11 +5940,11 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -5953,12 +5953,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5976,11 +5976,11 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -5989,12 +5989,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79468</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7J87D</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>SPM-01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6012,11 +6012,11 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -6025,12 +6025,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6048,11 +6048,11 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -6061,12 +6061,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6084,11 +6084,11 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -6097,12 +6097,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6120,11 +6120,11 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -6133,12 +6133,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA79475</t>
+          <t>FBA79492</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0DJFJZMC6</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>TIC-04</t>
+          <t>V-02</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6156,11 +6156,11 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -6169,22 +6169,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA79591</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0DM66B2DW</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -6205,22 +6205,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6228,11 +6228,11 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -6241,12 +6241,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6264,11 +6264,11 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -6277,12 +6277,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6300,11 +6300,11 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -6313,12 +6313,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79565</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DKJZDY72</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6336,11 +6336,11 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -6349,12 +6349,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79443</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LE-03</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6372,11 +6372,11 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -6385,12 +6385,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79687</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>MGC-03</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6408,11 +6408,11 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -6421,22 +6421,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA79596</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>MG-01</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6444,11 +6444,11 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -6457,12 +6457,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79381</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>ETR-06</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6480,11 +6480,11 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -6493,12 +6493,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA79333</t>
+          <t>FBA79467</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0D63DTKQB</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>HM-02</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6516,11 +6516,11 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -6529,12 +6529,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79265</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6552,11 +6552,11 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -6565,12 +6565,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79483</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DK9NRBWJ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6588,11 +6588,11 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -6601,22 +6601,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>ETC-07</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6624,11 +6624,11 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -6637,12 +6637,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79566</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>VC-05</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6660,11 +6660,11 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>179</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -6673,12 +6673,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6696,11 +6696,11 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -6709,22 +6709,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA79262</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0CYSMBCB8</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6732,11 +6732,11 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -6745,12 +6745,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79352</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0D637B562</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>WF-02-BL</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6768,11 +6768,11 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -6781,12 +6781,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA79599</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0DRD8J8R5</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VC-06</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -6804,11 +6804,11 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -6817,12 +6817,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6840,11 +6840,11 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -6853,12 +6853,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6876,11 +6876,11 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -6889,22 +6889,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6912,11 +6912,11 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -6925,12 +6925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -6948,11 +6948,11 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -6961,12 +6961,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -6984,11 +6984,11 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -6997,22 +6997,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7020,11 +7020,11 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7056,11 +7056,11 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -7069,12 +7069,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7092,11 +7092,11 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -7105,12 +7105,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA79599</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0DRD8J8R5</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VC-06</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7128,11 +7128,11 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -7141,12 +7141,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7164,11 +7164,11 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -7177,22 +7177,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7200,11 +7200,11 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -7213,12 +7213,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7236,11 +7236,11 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -7249,12 +7249,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7272,11 +7272,11 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -7285,12 +7285,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7308,11 +7308,11 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -7321,12 +7321,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79589</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7344,11 +7344,11 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -7357,12 +7357,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7380,11 +7380,11 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -7393,12 +7393,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7416,11 +7416,11 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -7429,12 +7429,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7452,11 +7452,11 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -7465,12 +7465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7488,11 +7488,11 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -7501,22 +7501,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7524,11 +7524,11 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -7537,22 +7537,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7560,11 +7560,11 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -7573,12 +7573,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7596,11 +7596,11 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -7609,22 +7609,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79475</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DJFJZMC6</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>TIC-04</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7632,11 +7632,11 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -7645,12 +7645,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79591</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DM66B2DW</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -7668,11 +7668,11 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -7681,12 +7681,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -7704,11 +7704,11 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -7717,12 +7717,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -7753,12 +7753,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -7776,11 +7776,11 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -7789,12 +7789,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FBA79693</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>B0DVC91Q7J</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -7812,11 +7812,11 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -7825,12 +7825,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79443</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>LE-03</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -7848,11 +7848,11 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -7861,12 +7861,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79687</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>MGC-03</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -7884,11 +7884,11 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -7897,12 +7897,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79596</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>MG-01</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7920,11 +7920,11 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -7933,12 +7933,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FBA79381</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ETR-06</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7956,11 +7956,11 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -7969,12 +7969,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FBA78996</t>
+          <t>FBA79333</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>B0CDQ6G4TC</t>
+          <t>B0D63DTKQB</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NP-03</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7992,11 +7992,11 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -8005,12 +8005,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8028,11 +8028,11 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8064,11 +8064,11 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,11 +8100,11 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8113,12 +8113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8136,11 +8136,11 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,11 +8172,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79262</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CYSMBCB8</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8208,11 +8208,11 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79352</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D637B562</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>WF-02-BL</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,11 +8244,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8257,12 +8257,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79599</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DRD8J8R5</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>VC-06</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8280,11 +8280,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -8293,12 +8293,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8316,7 +8316,7 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -8329,12 +8329,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA79266</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0D2LGR3GG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8352,7 +8352,7 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -8365,12 +8365,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -8401,12 +8401,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8424,7 +8424,7 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -8437,12 +8437,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79266</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0D2LGR3GG</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8460,7 +8460,7 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -8473,12 +8473,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8496,7 +8496,7 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -8509,12 +8509,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -8545,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8568,7 +8568,7 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -8581,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8604,7 +8604,7 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -8617,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,7 +8640,7 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -8689,12 +8689,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -8725,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79452</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VC-01</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8748,7 +8748,7 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -8761,12 +8761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79350</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -8797,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79452</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>VC-01</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -8833,12 +8833,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8856,7 +8856,7 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -8869,12 +8869,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8892,7 +8892,7 @@
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -8905,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79483</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DK9NRBWJ</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -8941,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -8977,14 +8977,10 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA79589</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>B0DNJP9T35</t>
-        </is>
-      </c>
+          <t>FBA80250</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -8992,7 +8988,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9000,11 +8996,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9013,14 +9009,10 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA79590</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>B0DM6BB3VT</t>
-        </is>
-      </c>
+          <t>FBA80251</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9028,7 +9020,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>VC-01 Pro</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9036,11 +9028,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9049,12 +9041,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA79333</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>B0D63DTKQB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9064,7 +9056,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>HM-02</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9072,11 +9064,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9085,12 +9077,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA79467</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9100,7 +9092,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9108,11 +9100,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>19</v>
+        <v>1002</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9121,12 +9113,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9136,7 +9128,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9144,11 +9136,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9157,12 +9149,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,7 +9164,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9180,11 +9172,11 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>78</v>
+        <v>1050</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9193,10 +9185,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA80250</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>FBA79991</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>B0GN85NZQN</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9204,7 +9200,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9212,11 +9208,11 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>500</v>
+        <v>459</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9225,10 +9221,14 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA80251</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
+          <t>FBA79991</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>B0GN85NZQN</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VC-01 Pro</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9244,7 +9244,7 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -9257,12 +9257,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9280,7 +9280,7 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -9293,12 +9293,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9316,11 +9316,11 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -9329,12 +9329,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9352,11 +9352,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9365,12 +9365,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>1050</v>
+        <v>3006</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -9401,12 +9401,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9424,11 +9424,11 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>459</v>
+        <v>1500</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9437,12 +9437,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9460,11 +9460,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>999</v>
+        <v>2000</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9473,12 +9473,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9496,7 +9496,7 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>2002</v>
+        <v>1000</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9545,12 +9545,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -9581,12 +9581,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9604,11 +9604,11 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>3006</v>
+        <v>1500</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -9617,14 +9617,10 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA79652</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9632,7 +9628,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9640,7 +9636,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9653,12 +9649,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9668,7 +9664,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9676,11 +9672,11 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -9689,12 +9685,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9704,7 +9700,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9712,11 +9708,11 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>1000</v>
+        <v>2004</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -9725,12 +9721,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9740,7 +9736,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9748,11 +9744,11 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -9761,12 +9757,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79993</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9776,7 +9772,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9784,7 +9780,7 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -9793,218 +9789,6 @@
       </c>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>FBA79984</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>B0GM1CZC7Y</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>MR-03</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>SP-02</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>FBA79406</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>B0DCK3N2JJ</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>HSB-04</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>FBA79439</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>MR-02</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>FBA79573</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>EA-02</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="n">
-        <v>1020</v>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>FBA79993</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="n">
-        <v>200</v>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L260"/>
+  <dimension ref="A1:L261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>987</v>
+        <v>962</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>888</v>
+        <v>428</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>585</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>40</v>
+        <v>681</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79572</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DKJVWM8Q</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>LE-07</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2245,12 +2245,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79572</t>
+          <t>FBA79569</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0DKJVWM8Q</t>
+          <t>B0DKJRML4K</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LE-07</t>
+          <t>LE-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2281,12 +2281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79569</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0DKJRML4K</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LE-06</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>403</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79443</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>LE-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>443</v>
+        <v>55</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79443</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LE-03</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>55</v>
+        <v>996</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2389,12 +2389,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>996</v>
+        <v>187</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2425,12 +2425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79591</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0DM66B2DW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>187</v>
+        <v>34</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2461,12 +2461,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA79591</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0DM66B2DW</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2497,12 +2497,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2533,12 +2533,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79571</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DKK12XWR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>IPL-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2569,12 +2569,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79571</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0DKK12XWR</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IPL-01</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>1359</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2641,12 +2641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79333</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D63DTKQB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>1433</v>
+        <v>20</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79333</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0D63DTKQB</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HM-02</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>35</v>
+        <v>503</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>543</v>
+        <v>924</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>924</v>
+        <v>4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2857,12 +2857,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>39</v>
+        <v>1119</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA78979</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0CDPQXPC1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>GS-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>1348</v>
+        <v>9</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2929,12 +2929,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA78979</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0CDPQXPC1</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>GS-01</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>944</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>994</v>
+        <v>170</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>170</v>
+        <v>715</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79375</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0CSG3FC4G</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>ET-03-BL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>805</v>
+        <v>39</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3073,12 +3073,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79375</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0CSG3FC4G</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ET-03-BL</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>39</v>
+        <v>458</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>458</v>
+        <v>16</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>82</v>
+        <v>991</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>1080</v>
+        <v>31</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3253,12 +3253,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>771</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3361,12 +3361,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79266</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D2LGR3GG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>771</v>
+        <v>9</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3397,12 +3397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79266</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0D2LGR3GG</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3433,12 +3433,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79273</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HS-02</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>282</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79265</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>282</v>
+        <v>113</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>113</v>
+        <v>452</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>452</v>
+        <v>53</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3577,12 +3577,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3613,12 +3613,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79684</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC9Q219</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>AP-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3721,12 +3721,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79684</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0DVC9Q219</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AP-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3757,12 +3757,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>369</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3793,12 +3793,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79693</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC91Q7J</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3829,22 +3829,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79693</t>
+          <t>FBA79003</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0DVC91Q7J</t>
+          <t>B0CFH6C6YM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>TR-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79003</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0CFH6C6YM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TR-05</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>65</v>
+        <v>275</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1122</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>1146</v>
+        <v>922</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3973,12 +3973,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>955</v>
+        <v>2453</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4009,12 +4009,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>2503</v>
+        <v>546</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4045,12 +4045,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>578</v>
+        <v>1593</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>1593</v>
+        <v>2643</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4117,12 +4117,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79849</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>CFM-03</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>2693</v>
+        <v>12</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4153,12 +4153,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79849</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CFM-03</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79988</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>AP-04</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>399</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4225,12 +4225,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79988</t>
+          <t>FBA79989</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AP-04</t>
+          <t>CAP-05</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>399</v>
+        <v>356</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4261,12 +4261,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79989</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CAP-05</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>356</v>
+        <v>12</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4297,12 +4297,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79992</t>
+          <t>FBA79993</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4320,7 +4320,7 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4333,12 +4333,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4369,12 +4369,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4405,22 +4405,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79984</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4428,11 +4428,11 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -4441,12 +4441,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4477,12 +4477,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4536,7 +4536,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4549,12 +4549,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4572,7 +4572,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4585,22 +4585,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4621,22 +4621,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4693,12 +4693,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79599</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0DRD8J8R5</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>VC-06</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4716,7 +4716,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4729,12 +4729,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79599</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0DRD8J8R5</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VC-06</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -4765,12 +4765,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -4801,12 +4801,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -4837,12 +4837,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4873,12 +4873,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79474</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>TIC-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -4909,12 +4909,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4945,12 +4945,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -4981,12 +4981,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5017,12 +5017,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5053,12 +5053,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5076,7 +5076,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5125,12 +5125,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5161,22 +5161,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5184,7 +5184,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -5197,22 +5197,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5233,22 +5233,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -5269,12 +5269,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5292,7 +5292,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -5305,12 +5305,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5341,12 +5341,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5377,12 +5377,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79693</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0DVC91Q7J</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5413,12 +5413,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79693</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0DVC91Q7J</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -5449,12 +5449,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5485,12 +5485,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -5521,12 +5521,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79381</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>ETR-06</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -5557,12 +5557,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79381</t>
+          <t>FBA78996</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0CDQ6G4TC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ETR-06</t>
+          <t>NP-03</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5593,12 +5593,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA78996</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0CDQ6G4TC</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NP-03</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5616,7 +5616,7 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -5629,12 +5629,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5665,12 +5665,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -5701,12 +5701,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -5737,12 +5737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -5773,12 +5773,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79273</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>HS-02</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -5832,7 +5832,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -5845,12 +5845,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79598</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>BM-02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -5917,12 +5917,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA79598</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>BM-02</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -5953,12 +5953,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79468</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DCK7J87D</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>SPM-01</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5976,7 +5976,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -5989,12 +5989,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA79468</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0DCK7J87D</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SPM-01</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -6025,12 +6025,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -6061,12 +6061,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6084,7 +6084,7 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -6097,12 +6097,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79492</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>V-02</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6133,22 +6133,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA79492</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>V-02</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -6169,12 +6169,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -6205,22 +6205,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -6241,12 +6241,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -6277,12 +6277,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79565</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DKJZDY72</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6300,7 +6300,7 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -6313,12 +6313,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA79565</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0DKJZDY72</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VC-04</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6336,7 +6336,7 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -6349,12 +6349,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6372,7 +6372,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -6385,22 +6385,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6408,7 +6408,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -6421,22 +6421,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79381</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>ETR-06</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6444,7 +6444,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>195</v>
+        <v>59</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -6457,12 +6457,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79381</t>
+          <t>FBA79467</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ETR-06</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -6493,12 +6493,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA79467</t>
+          <t>FBA79265</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -6529,12 +6529,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBA79483</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DK9NRBWJ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -6565,22 +6565,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>ETC-07</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6588,7 +6588,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -6601,22 +6601,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79566</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>VC-05</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -6637,12 +6637,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -6673,22 +6673,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -6709,22 +6709,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -6745,12 +6745,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6768,7 +6768,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -6781,12 +6781,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -6804,7 +6804,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -6817,12 +6817,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6840,7 +6840,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -6853,22 +6853,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6876,7 +6876,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -6889,22 +6889,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6912,7 +6912,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -6925,12 +6925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -6948,7 +6948,7 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -6984,7 +6984,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -6997,12 +6997,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7020,7 +7020,7 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -7033,12 +7033,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -7105,12 +7105,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7128,7 +7128,7 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -7141,22 +7141,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7164,7 +7164,7 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -7177,22 +7177,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -7213,12 +7213,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -7249,12 +7249,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -7285,12 +7285,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79589</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7308,7 +7308,7 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -7321,12 +7321,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79589</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -7357,12 +7357,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7380,7 +7380,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -7393,12 +7393,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7416,7 +7416,7 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -7429,12 +7429,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -7465,12 +7465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7488,7 +7488,7 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -7501,12 +7501,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7524,7 +7524,7 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -7537,12 +7537,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7560,7 +7560,7 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -7573,12 +7573,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79475</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DJFJZMC6</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>TIC-04</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -7609,12 +7609,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FBA79475</t>
+          <t>FBA79591</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>B0DJFJZMC6</t>
+          <t>B0DM66B2DW</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>TIC-04</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7632,7 +7632,7 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -7645,12 +7645,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FBA79591</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B0DM66B2DW</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -7668,7 +7668,7 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -7681,12 +7681,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -7704,7 +7704,7 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -7717,12 +7717,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -7740,7 +7740,7 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -7753,12 +7753,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -7776,7 +7776,7 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -7789,12 +7789,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79443</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>LE-03</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -7812,7 +7812,7 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -7825,12 +7825,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FBA79443</t>
+          <t>FBA79687</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LE-03</t>
+          <t>MGC-03</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -7848,7 +7848,7 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -7861,12 +7861,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FBA79687</t>
+          <t>FBA79596</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>MGC-03</t>
+          <t>MG-01</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -7897,12 +7897,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FBA79596</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MG-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7920,7 +7920,7 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -7933,12 +7933,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79333</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D63DTKQB</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -7969,12 +7969,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FBA79333</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>B0D63DTKQB</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>HM-02</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7992,7 +7992,7 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -8005,12 +8005,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8028,7 +8028,7 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -8041,12 +8041,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,7 +8100,7 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -8113,12 +8113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8136,7 +8136,7 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA79262</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CYSMBCB8</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,7 +8172,7 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -8185,12 +8185,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FBA79262</t>
+          <t>FBA79352</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B0CYSMBCB8</t>
+          <t>B0D637B562</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>WF-02-BL</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA79352</t>
+          <t>FBA79599</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0D637B562</t>
+          <t>B0DRD8J8R5</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>WF-02-BL</t>
+          <t>VC-06</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,7 +8244,7 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -8257,14 +8257,10 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA79599</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>B0DRD8J8R5</t>
-        </is>
-      </c>
+          <t>FBA80250</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -8272,7 +8268,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VC-06</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8280,11 +8276,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>7</v>
+        <v>500</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -8293,14 +8289,10 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA79279</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>B0D8445KJN</t>
-        </is>
-      </c>
+          <t>FBA80251</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -8308,7 +8300,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>VC-01 Pro</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8316,11 +8308,11 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>108</v>
+        <v>1000</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -8329,12 +8321,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8344,7 +8336,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8352,11 +8344,11 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>132</v>
+        <v>2000</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -8365,12 +8357,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8380,7 +8372,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8388,11 +8380,11 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
-        <v>60</v>
+        <v>575</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -8401,12 +8393,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8416,7 +8408,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8424,11 +8416,11 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>147</v>
+        <v>1440</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -8437,12 +8429,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA79266</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0D2LGR3GG</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8452,7 +8444,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8460,11 +8452,11 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -8473,12 +8465,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8488,7 +8480,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8496,11 +8488,11 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>100</v>
+        <v>1002</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -8509,12 +8501,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8524,7 +8516,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8532,11 +8524,11 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -8545,12 +8537,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8552,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8568,11 +8560,11 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -8581,12 +8573,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8588,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8604,11 +8596,11 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>11</v>
+        <v>561</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -8617,12 +8609,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8624,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,11 +8632,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>100</v>
+        <v>252</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -8653,12 +8645,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8660,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,11 +8668,11 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>43</v>
+        <v>999</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -8689,12 +8681,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8704,7 +8696,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8712,11 +8704,11 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -8725,12 +8717,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8732,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8748,11 +8740,11 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>91</v>
+        <v>500</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -8761,12 +8753,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8776,7 +8768,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8784,11 +8776,11 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -8797,12 +8789,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79452</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8804,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VC-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,11 +8812,11 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>30</v>
+        <v>1052</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -8833,12 +8825,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8848,7 +8840,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8856,11 +8848,11 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -8892,11 +8884,11 @@
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
-        <v>13</v>
+        <v>2000</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -8905,12 +8897,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8912,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,11 +8920,11 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -8941,12 +8933,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8948,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,11 +8956,11 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>52</v>
+        <v>2004</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -8977,10 +8969,14 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA80250</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr"/>
+          <t>FBA79652</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
       <c r="C238" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -8988,7 +8984,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -8996,11 +8992,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>500</v>
+        <v>1002</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9009,10 +9005,14 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA80251</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
+          <t>FBA79692</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
       <c r="C239" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VC-01 Pro</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9028,7 +9028,7 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -9041,12 +9041,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9077,12 +9077,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9100,11 +9100,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>1002</v>
+        <v>500</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9113,12 +9113,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9149,12 +9149,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9172,7 +9172,7 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -9185,12 +9185,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9208,11 +9208,11 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>459</v>
+        <v>1000</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9221,12 +9221,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9244,11 +9244,11 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -9257,12 +9257,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9280,11 +9280,11 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>2002</v>
+        <v>1500</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9293,14 +9293,10 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA79567</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
+          <t>FBA80294</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9308,7 +9304,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>AP-06</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9316,7 +9312,7 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -9329,14 +9325,10 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA79590</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>B0DM6BB3VT</t>
-        </is>
-      </c>
+          <t>FBA80295</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9344,7 +9336,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>AP-07</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9352,11 +9344,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9365,14 +9357,10 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA79652</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
+          <t>FBA80296</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9380,7 +9368,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9388,11 +9376,11 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>3006</v>
+        <v>500</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -9401,14 +9389,10 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA79652</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>B0F43P6D23</t>
-        </is>
-      </c>
+          <t>FBA80297</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9416,7 +9400,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>ST-05</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9424,7 +9408,7 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -9437,14 +9421,10 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA79812</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
+          <t>FBA80298</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9452,7 +9432,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>DM-01</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9460,11 +9440,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9473,14 +9453,10 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA79570</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>B0DKJXRXKM</t>
-        </is>
-      </c>
+          <t>FBA80300</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9488,7 +9464,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9496,11 +9472,11 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -9509,14 +9485,10 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80301</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9524,7 +9496,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>FM-02</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9532,11 +9504,11 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>1000</v>
+        <v>102</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9545,14 +9517,10 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9560,7 +9528,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9568,11 +9536,11 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -9581,14 +9549,10 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA79984</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>B0GM1CZC7Y</t>
-        </is>
-      </c>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9596,7 +9560,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9604,11 +9568,11 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -9636,11 +9600,11 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -9708,11 +9672,11 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>2004</v>
+        <v>500</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -9721,12 +9685,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9736,7 +9700,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9744,11 +9708,11 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>1020</v>
+        <v>1500</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -9780,15 +9744,51 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ST-03</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="n">
+        <v>148</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L261"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8465,12 +8465,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8488,7 +8488,7 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>1002</v>
+        <v>239</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -8537,12 +8537,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -8573,12 +8573,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8596,11 +8596,11 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>561</v>
+        <v>999</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -8609,12 +8609,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8632,7 +8632,7 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -8645,12 +8645,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8668,11 +8668,11 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -8681,12 +8681,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8704,7 +8704,7 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>207</v>
+        <v>2000</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -8717,12 +8717,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8740,7 +8740,7 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8776,7 +8776,7 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>450</v>
+        <v>2004</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -8789,12 +8789,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8812,11 +8812,11 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>1052</v>
+        <v>999</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -8825,12 +8825,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8848,7 +8848,7 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8884,7 +8884,7 @@
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -8897,12 +8897,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8920,7 +8920,7 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -8933,12 +8933,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8956,11 +8956,11 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>2004</v>
+        <v>1000</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -8969,12 +8969,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -8992,11 +8992,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>1002</v>
+        <v>1500</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9005,14 +9005,10 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA79692</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>B0DVC58QPZ</t>
-        </is>
-      </c>
+          <t>FBA80332</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9020,7 +9016,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>ST-06</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9028,7 +9024,7 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>999</v>
+        <v>200</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -9041,14 +9037,10 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA79812</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
+          <t>FBA80333</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9056,7 +9048,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>CG-01</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9064,11 +9056,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9077,14 +9069,10 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA79992</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>B0GN94YDY2</t>
-        </is>
-      </c>
+          <t>FBA80334</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9092,7 +9080,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>SJ-01</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9100,7 +9088,7 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -9113,14 +9101,10 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA79570</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>B0DKJXRXKM</t>
-        </is>
-      </c>
+          <t>FBA80294</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9128,7 +9112,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>AP-06</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9136,11 +9120,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9149,14 +9133,10 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80295</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9164,7 +9144,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>AP-07</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9176,7 +9156,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9185,14 +9165,10 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80296</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9200,7 +9176,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9208,7 +9184,7 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -9221,14 +9197,10 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80297</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9236,7 +9208,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>ST-05</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9244,11 +9216,11 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -9257,14 +9229,10 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA79984</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>B0GM1CZC7Y</t>
-        </is>
-      </c>
+          <t>FBA80298</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9272,7 +9240,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>DM-01</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9280,7 +9248,7 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -9293,7 +9261,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA80294</t>
+          <t>FBA80300</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -9304,7 +9272,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AP-06</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9312,7 +9280,7 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>500</v>
+        <v>1008</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -9325,7 +9293,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA80295</t>
+          <t>FBA80301</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -9336,7 +9304,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>AP-07</t>
+          <t>FM-02</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9344,7 +9312,7 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>1000</v>
+        <v>102</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -9357,7 +9325,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA80296</t>
+          <t>FBA80215</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -9368,7 +9336,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ST-04</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9376,11 +9344,11 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -9389,7 +9357,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA80297</t>
+          <t>FBA80215</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -9400,7 +9368,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9408,11 +9376,11 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9421,7 +9389,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA80298</t>
+          <t>FBA80215</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -9432,7 +9400,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>DM-01</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9440,11 +9408,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9453,10 +9421,14 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA80300</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>FBA79406</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>B0DCK3N2JJ</t>
+        </is>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9464,7 +9436,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9472,7 +9444,7 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -9485,10 +9457,14 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA80301</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr"/>
+          <t>FBA79439</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
       <c r="C253" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9496,7 +9472,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>FM-02</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9504,11 +9480,11 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>102</v>
+        <v>500</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9517,10 +9493,14 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr"/>
+          <t>FBA79439</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
       <c r="C254" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9528,7 +9508,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9536,7 +9516,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -9549,10 +9529,14 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
       <c r="C255" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9560,7 +9544,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9568,7 +9552,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -9581,10 +9565,14 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9592,7 +9580,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9600,7 +9588,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>500</v>
+        <v>148</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9609,186 +9597,6 @@
       </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>FBA79406</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>B0DCK3N2JJ</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>HSB-04</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>FBA79439</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>MR-02</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="n">
-        <v>500</v>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>FBA79439</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>MR-02</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>FBA79993</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="n">
-        <v>52</v>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>FBA79993</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="n">
-        <v>148</v>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L256"/>
+  <dimension ref="A1:L287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>1204</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>460</v>
+        <v>391</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>627</v>
+        <v>587</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>549</v>
+        <v>507</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>962</v>
+        <v>755</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>428</v>
+        <v>123</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>754</v>
+        <v>694</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>681</v>
+        <v>195</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>996</v>
+        <v>896</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2569,12 +2569,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>12</v>
+        <v>1263</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79333</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D63DTKQB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>1359</v>
+        <v>21</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2641,12 +2641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79333</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0D63DTKQB</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HM-02</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>463</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>503</v>
+        <v>920</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>924</v>
+        <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>39</v>
+        <v>657</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2857,12 +2857,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA78979</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0CDPQXPC1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>GS-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>1119</v>
+        <v>9</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA78979</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0CDPQXPC1</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>GS-01</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>924</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2929,12 +2929,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>944</v>
+        <v>170</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>170</v>
+        <v>685</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79375</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0CSG3FC4G</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>ET-03-BL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>715</v>
+        <v>39</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79375</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0CSG3FC4G</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ET-03-BL</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>39</v>
+        <v>358</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3073,12 +3073,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>458</v>
+        <v>16</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>82</v>
+        <v>971</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>991</v>
+        <v>31</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3253,12 +3253,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>751</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79266</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D2LGR3GG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>771</v>
+        <v>9</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3361,12 +3361,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79266</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0D2LGR3GG</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3397,12 +3397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79273</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>HS-02</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>281</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3433,12 +3433,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79265</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>282</v>
+        <v>113</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>113</v>
+        <v>403</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>452</v>
+        <v>53</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3577,12 +3577,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3613,12 +3613,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79684</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC9Q219</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>AP-02</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79684</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0DVC9Q219</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AP-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3721,12 +3721,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>369</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3757,12 +3757,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79693</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC91Q7J</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3793,22 +3793,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79693</t>
+          <t>FBA79003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0DVC91Q7J</t>
+          <t>B0CFH6C6YM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>TR-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3829,12 +3829,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79003</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0CFH6C6YM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TR-05</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>275</v>
+        <v>1122</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>1122</v>
+        <v>922</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-07</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>922</v>
+        <v>2403</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3973,12 +3973,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>2453</v>
+        <v>1973</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>1593</v>
+        <v>1528</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>2643</v>
+        <v>2543</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4405,12 +4405,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4428,11 +4428,11 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -4441,12 +4441,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4464,11 +4464,11 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -4477,12 +4477,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4500,11 +4500,11 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -4513,12 +4513,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4536,11 +4536,11 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -4549,12 +4549,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79598</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>BM-02</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4572,11 +4572,11 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -4585,22 +4585,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4608,11 +4608,11 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -4621,12 +4621,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79468</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0DCK7J87D</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>SPM-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4644,11 +4644,11 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -4657,12 +4657,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4680,11 +4680,11 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -4693,12 +4693,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79599</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0DRD8J8R5</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VC-06</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4716,11 +4716,11 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -4729,12 +4729,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -4752,11 +4752,11 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -4765,12 +4765,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79492</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>V-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4788,11 +4788,11 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -4801,22 +4801,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4824,11 +4824,11 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -4837,22 +4837,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4860,11 +4860,11 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -4873,12 +4873,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4896,11 +4896,11 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -4909,12 +4909,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4932,11 +4932,11 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -4945,12 +4945,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79565</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0DKJZDY72</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4968,11 +4968,11 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -4981,12 +4981,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5004,11 +5004,11 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -5017,12 +5017,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5040,11 +5040,11 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -5053,22 +5053,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5076,11 +5076,11 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>9</v>
+        <v>195</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -5089,22 +5089,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79381</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>ETR-06</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5112,11 +5112,11 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -5125,22 +5125,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79467</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5148,11 +5148,11 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -5161,12 +5161,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79265</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>CR-01</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5184,11 +5184,11 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -5197,22 +5197,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79483</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DK9NRBWJ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5220,11 +5220,11 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -5233,22 +5233,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>ETC-07</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5256,11 +5256,11 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -5269,12 +5269,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79566</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>VC-05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5292,11 +5292,11 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>6</v>
+        <v>179</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -5305,12 +5305,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5328,11 +5328,11 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -5341,22 +5341,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5364,11 +5364,11 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -5377,12 +5377,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79693</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0DVC91Q7J</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>TM-05</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5400,11 +5400,11 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -5413,12 +5413,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -5436,11 +5436,11 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -5449,12 +5449,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5472,11 +5472,11 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -5485,12 +5485,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5508,11 +5508,11 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -5521,22 +5521,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79381</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ETR-06</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5544,11 +5544,11 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -5557,12 +5557,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA78996</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0CDQ6G4TC</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NP-03</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5580,11 +5580,11 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -5593,12 +5593,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5616,11 +5616,11 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -5629,12 +5629,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5652,11 +5652,11 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -5665,12 +5665,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5688,11 +5688,11 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -5701,12 +5701,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -5724,11 +5724,11 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -5737,12 +5737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -5773,12 +5773,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79273</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>HS-02</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -5809,22 +5809,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -5832,7 +5832,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -5845,12 +5845,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79351</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79598</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>BM-02</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -5917,12 +5917,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -5953,12 +5953,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA79468</t>
+          <t>FBA79589</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0DCK7J87D</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SPM-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5976,7 +5976,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -5989,12 +5989,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -6025,12 +6025,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -6061,12 +6061,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6084,7 +6084,7 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -6097,12 +6097,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79492</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>V-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -6133,22 +6133,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D842173P</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -6169,22 +6169,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -6205,12 +6205,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -6241,12 +6241,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79475</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DJFJZMC6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>TIC-04</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -6277,12 +6277,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA79565</t>
+          <t>FBA79591</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0DKJZDY72</t>
+          <t>B0DM66B2DW</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VC-04</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6300,7 +6300,7 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -6313,12 +6313,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6336,7 +6336,7 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -6349,12 +6349,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79677</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0DVCBR11D</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NP-06</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6372,7 +6372,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -6385,22 +6385,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6408,7 +6408,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>195</v>
+        <v>9</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -6421,12 +6421,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA79381</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ETR-06</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6444,7 +6444,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -6457,12 +6457,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79467</t>
+          <t>FBA79443</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>TM-01</t>
+          <t>LE-03</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -6493,12 +6493,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBA79687</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>MGC-03</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -6529,12 +6529,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79596</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>MG-01</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -6565,22 +6565,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6588,7 +6588,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -6601,12 +6601,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79333</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0D63DTKQB</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -6637,12 +6637,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -6673,22 +6673,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -6709,12 +6709,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -6745,12 +6745,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6768,7 +6768,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -6781,12 +6781,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -6804,7 +6804,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -6817,12 +6817,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79262</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0CYSMBCB8</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6840,7 +6840,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -6853,22 +6853,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79810</t>
+          <t>FBA79352</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D637B562</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>MF-01</t>
+          <t>WF-02-BL</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6876,7 +6876,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -6889,12 +6889,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79599</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DRD8J8R5</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>VC-06</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6912,7 +6912,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -6925,12 +6925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -6948,11 +6948,11 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -6961,12 +6961,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -6984,11 +6984,11 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -6997,12 +6997,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7020,11 +7020,11 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA78995</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>NP-02</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7056,11 +7056,11 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -7069,12 +7069,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7092,11 +7092,11 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -7105,22 +7105,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79810</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>MF-01</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7128,11 +7128,11 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -7141,22 +7141,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nexlev </t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7164,11 +7164,11 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -7177,12 +7177,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7200,11 +7200,11 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -7213,12 +7213,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79599</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DRD8J8R5</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>VC-06</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7236,11 +7236,11 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -7249,12 +7249,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7272,11 +7272,11 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -7285,12 +7285,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79589</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7308,11 +7308,11 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -7321,12 +7321,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7344,11 +7344,11 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -7357,12 +7357,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7380,11 +7380,11 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -7393,12 +7393,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA78995</t>
+          <t>FBA79474</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NP-02</t>
+          <t>TIC-03</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7416,11 +7416,11 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -7429,12 +7429,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7452,11 +7452,11 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -7465,12 +7465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBK79347</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0D842173P</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ETC-05-PI</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7488,11 +7488,11 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -7501,12 +7501,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7524,11 +7524,11 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -7537,12 +7537,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7560,11 +7560,11 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -7573,12 +7573,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FBA79475</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B0DJFJZMC6</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>TIC-04</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7596,11 +7596,11 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -7609,22 +7609,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FBA79591</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>B0DM66B2DW</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7632,11 +7632,11 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -7645,22 +7645,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -7668,11 +7668,11 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -7681,12 +7681,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -7704,11 +7704,11 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -7717,22 +7717,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t xml:space="preserve">Nexlev </t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>ETC-08</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -7753,12 +7753,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -7776,11 +7776,11 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -7789,12 +7789,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FBA79443</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LE-03</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -7812,11 +7812,11 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -7825,12 +7825,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FBA79687</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>MGC-03</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -7848,11 +7848,11 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -7861,12 +7861,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FBA79596</t>
+          <t>FBA79351</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>MG-01</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -7884,11 +7884,11 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -7897,12 +7897,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79693</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC91Q7J</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>TM-05</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7920,11 +7920,11 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -7933,12 +7933,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FBA79333</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>B0D63DTKQB</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>HM-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7956,11 +7956,11 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -7969,12 +7969,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FBA79348</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7992,11 +7992,11 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -8005,12 +8005,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8028,11 +8028,11 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79381</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>ETR-06</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8064,11 +8064,11 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA78996</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CDQ6G4TC</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>NP-03</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,11 +8100,11 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8113,12 +8113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8136,11 +8136,11 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA79262</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0CYSMBCB8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,11 +8172,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FBA79352</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B0D637B562</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>WF-02-BL</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8208,11 +8208,11 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA79599</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0DRD8J8R5</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VC-06</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,11 +8244,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8257,10 +8257,14 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA80250</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr"/>
+          <t>FBA79279</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>B0D8445KJN</t>
+        </is>
+      </c>
       <c r="C218" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -8268,7 +8272,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8276,11 +8280,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>500</v>
+        <v>147</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -8289,10 +8293,14 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA80251</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
+          <t>FBA79268</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -8300,7 +8308,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VC-01 Pro</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8308,11 +8316,11 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>1000</v>
+        <v>115</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -8321,12 +8329,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8336,7 +8344,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8344,11 +8352,11 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>2000</v>
+        <v>41</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -8357,12 +8365,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8372,7 +8380,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8380,11 +8388,11 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
-        <v>575</v>
+        <v>36</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -8393,12 +8401,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8408,7 +8416,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8416,11 +8424,11 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>1440</v>
+        <v>131</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -8429,12 +8437,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79266</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LGR3GG</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8444,7 +8452,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8452,11 +8460,11 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -8465,12 +8473,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8480,7 +8488,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8488,11 +8496,11 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -8501,12 +8509,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8516,7 +8524,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8524,11 +8532,11 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -8537,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79677</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0DVCBR11D</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8552,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>NP-06</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8560,11 +8568,11 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>252</v>
+        <v>13</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -8573,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8588,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8596,11 +8604,11 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>999</v>
+        <v>30</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -8609,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8624,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8632,11 +8640,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>500</v>
+        <v>124</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -8645,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8660,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8668,11 +8676,11 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>1000</v>
+        <v>51</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -8681,12 +8689,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8696,7 +8704,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8704,11 +8712,11 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>2000</v>
+        <v>16</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -8717,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8732,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8740,11 +8748,11 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>1500</v>
+        <v>163</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -8753,12 +8761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79350</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8768,7 +8776,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8776,11 +8784,11 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>2004</v>
+        <v>123</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -8789,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8804,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8812,11 +8820,11 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>999</v>
+        <v>18</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -8825,12 +8833,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA79992</t>
+          <t>FBA79452</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8840,7 +8848,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>VC-01</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8848,11 +8856,11 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -8861,12 +8869,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8876,7 +8884,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8884,11 +8892,11 @@
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
-        <v>1000</v>
+        <v>62</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -8897,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79474</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8912,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>TIC-03</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8920,11 +8928,11 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -8933,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8948,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8956,11 +8964,11 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -8969,12 +8977,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA79984</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8984,7 +8992,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -8992,11 +9000,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>1500</v>
+        <v>3</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9005,10 +9013,14 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA80332</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
+          <t>FBA79570</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>B0DKJXRXKM</t>
+        </is>
+      </c>
       <c r="C239" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9016,7 +9028,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ST-06</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9024,11 +9036,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9037,10 +9049,14 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA80333</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
+          <t>FBA79573</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
       <c r="C240" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9048,7 +9064,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>CG-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9056,11 +9072,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9069,10 +9085,14 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA80334</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr"/>
+          <t>FBA79589</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>B0DNJP9T35</t>
+        </is>
+      </c>
       <c r="C241" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9080,7 +9100,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SJ-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9088,11 +9108,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9101,10 +9121,14 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA80294</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr"/>
+          <t>FBA79590</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
       <c r="C242" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9112,7 +9136,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AP-06</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9120,11 +9144,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9133,10 +9157,14 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA80295</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr"/>
+          <t>FBA79333</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>B0D63DTKQB</t>
+        </is>
+      </c>
       <c r="C243" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9144,7 +9172,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AP-07</t>
+          <t>HM-02</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9152,11 +9180,11 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9165,10 +9193,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA80296</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>FBA79467</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>B0DK9LYT4P</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9176,7 +9208,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ST-04</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9184,11 +9216,11 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>500</v>
+        <v>69</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9197,10 +9229,14 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA80297</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
+          <t>FBA79483</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>B0DK9NRBWJ</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9208,7 +9244,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>TM-03</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9216,11 +9252,11 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -9229,10 +9265,14 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA80298</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr"/>
+          <t>FBA79809</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>B0FJ8SFNRH</t>
+        </is>
+      </c>
       <c r="C246" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9240,7 +9280,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>DM-01</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9248,11 +9288,11 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>300</v>
+        <v>24</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9261,10 +9301,14 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA80300</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
+          <t>FBA79819</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>B0FT8R24QM</t>
+        </is>
+      </c>
       <c r="C247" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9272,7 +9316,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9280,11 +9324,11 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>1008</v>
+        <v>74</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -9293,10 +9337,14 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA80301</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr"/>
+          <t>FBA79707</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
       <c r="C248" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9304,7 +9352,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>FM-02</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9312,11 +9360,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9325,7 +9373,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA80215</t>
+          <t>FBA80250</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -9336,7 +9384,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9344,7 +9392,7 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -9357,7 +9405,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA80215</t>
+          <t>FBA80251</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -9368,7 +9416,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>VC-01 Pro</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9376,11 +9424,11 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9389,10 +9437,14 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr"/>
+          <t>FBA78981</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
       <c r="C251" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9400,7 +9452,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9408,11 +9460,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9421,12 +9473,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9436,7 +9488,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9444,11 +9496,11 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>1000</v>
+        <v>575</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -9457,12 +9509,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9472,7 +9524,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9480,7 +9532,7 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>500</v>
+        <v>1440</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -9493,12 +9545,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9508,7 +9560,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9516,7 +9568,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -9529,12 +9581,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9544,7 +9596,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9552,7 +9604,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>52</v>
+        <v>239</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -9565,12 +9617,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9580,7 +9632,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9588,7 +9640,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>148</v>
+        <v>250</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9597,6 +9649,1070 @@
       </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>FBA79991</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>B0GN85NZQN</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DH-01</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>252</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>FBA79991</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>B0GN85NZQN</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DH-01</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>999</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>FBA79567</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="n">
+        <v>500</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>FBA79567</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>FBA79590</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CFM-01</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>FBA79652</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>FBA79652</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="n">
+        <v>2004</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FBA79692</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>AP-03</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="n">
+        <v>999</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>FBA79992</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>B0GN94YDY2</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ST-02</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="n">
+        <v>500</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FBA79570</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>B0DKJXRXKM</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>BR-01</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FBA79971</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SP-01</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FBA79971</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SP-01</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FBA79984</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>B0GM1CZC7Y</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>MR-03</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FBA80332</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ST-06</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="n">
+        <v>200</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FBA80333</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CG-01</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="n">
+        <v>100</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FBA80334</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>SJ-01</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="n">
+        <v>200</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FBA80294</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AP-06</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="n">
+        <v>500</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FBA80295</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>AP-07</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FBA80296</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ST-04</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>500</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>FBA80297</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ST-05</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="n">
+        <v>300</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>FBA80298</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DM-01</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="n">
+        <v>300</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>FBA80300</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>KM-01</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="n">
+        <v>1008</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FBA80301</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>FM-02</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>102</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SP-02</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="n">
+        <v>250</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SP-02</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="n">
+        <v>250</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SP-02</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="n">
+        <v>500</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>FBA79406</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>B0DCK3N2JJ</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>HSB-04</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>FBA79439</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>MR-02</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="n">
+        <v>500</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>FBA79439</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>MR-02</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ST-03</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="n">
+        <v>52</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ST-03</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="n">
+        <v>148</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/inventory_snapshot_nexlev.xlsx
+++ b/data/input/inventory_snapshot_nexlev.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L287"/>
+  <dimension ref="A1:L283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9509,12 +9509,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9532,7 +9532,7 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>1440</v>
+        <v>1002</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -9545,12 +9545,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>1000</v>
+        <v>239</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -9581,12 +9581,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9604,7 +9604,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>239</v>
+        <v>999</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -9617,12 +9617,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9640,7 +9640,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9653,12 +9653,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9676,7 +9676,7 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>252</v>
+        <v>2000</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -9689,12 +9689,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9712,11 +9712,11 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>999</v>
+        <v>1500</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -9725,12 +9725,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9748,11 +9748,11 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>500</v>
+        <v>999</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -9761,12 +9761,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9784,11 +9784,11 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -9797,12 +9797,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9820,7 +9820,7 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -9833,12 +9833,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9856,7 +9856,7 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -9869,12 +9869,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -9892,11 +9892,11 @@
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
-        <v>2004</v>
+        <v>1000</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -9905,12 +9905,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -9928,11 +9928,11 @@
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -9941,12 +9941,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FBA79992</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -9964,11 +9964,11 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -9977,14 +9977,10 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FBA79570</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>B0DKJXRXKM</t>
-        </is>
-      </c>
+          <t>FBA80332</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -9992,7 +9988,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>ST-06</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -10000,11 +9996,11 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -10013,14 +10009,10 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80333</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10028,7 +10020,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>CG-01</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -10036,11 +10028,11 @@
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -10049,14 +10041,10 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>FBA79971</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>B0GGHZWMVW</t>
-        </is>
-      </c>
+          <t>FBA80334</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10064,7 +10052,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SJ-01</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -10072,7 +10060,7 @@
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -10085,14 +10073,10 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>FBA79984</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>B0GM1CZC7Y</t>
-        </is>
-      </c>
+          <t>FBA80294</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10100,7 +10084,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>AP-06</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -10108,7 +10092,7 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -10121,7 +10105,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>FBA80332</t>
+          <t>FBA80295</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -10132,7 +10116,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ST-06</t>
+          <t>AP-07</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -10140,7 +10124,7 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -10153,7 +10137,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FBA80333</t>
+          <t>FBA80296</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -10164,7 +10148,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>CG-01</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -10172,7 +10156,7 @@
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -10185,7 +10169,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>FBA80334</t>
+          <t>FBA80297</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -10196,7 +10180,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>SJ-01</t>
+          <t>ST-05</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -10204,7 +10188,7 @@
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -10217,7 +10201,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>FBA80294</t>
+          <t>FBA80298</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -10228,7 +10212,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>AP-06</t>
+          <t>DM-01</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -10236,7 +10220,7 @@
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -10249,7 +10233,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>FBA80295</t>
+          <t>FBA80300</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -10260,7 +10244,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>AP-07</t>
+          <t>KM-01</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -10268,7 +10252,7 @@
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -10281,7 +10265,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>FBA80296</t>
+          <t>FBA80301</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -10292,7 +10276,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ST-04</t>
+          <t>FM-02</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -10300,7 +10284,7 @@
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="n">
-        <v>500</v>
+        <v>102</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -10313,10 +10297,14 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>FBA80297</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
+          <t>FBA80215</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>B0HGDWGKP9</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10324,7 +10312,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -10332,11 +10320,11 @@
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -10345,7 +10333,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>FBA80298</t>
+          <t>FBA80215</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -10356,7 +10344,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DM-01</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -10364,11 +10352,11 @@
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -10377,10 +10365,14 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>FBA80300</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr"/>
+          <t>FBA79406</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>B0DCK3N2JJ</t>
+        </is>
+      </c>
       <c r="C278" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10388,7 +10380,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -10396,7 +10388,7 @@
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -10409,10 +10401,14 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>FBA80301</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr"/>
+          <t>FBA79439</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
       <c r="C279" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10420,7 +10416,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>FM-02</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -10428,11 +10424,11 @@
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
-        <v>102</v>
+        <v>500</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -10441,10 +10437,14 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
+          <t>FBA79439</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
       <c r="C280" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -10460,7 +10460,7 @@
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="n">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -10473,10 +10473,14 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>FBA79573</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
       <c r="C281" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10484,7 +10488,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -10492,7 +10496,7 @@
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="n">
-        <v>250</v>
+        <v>1020</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -10505,10 +10509,14 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>FBA80215</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
       <c r="C282" t="inlineStr">
         <is>
           <t>Nexlev</t>
@@ -10516,7 +10524,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -10524,7 +10532,7 @@
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="n">
-        <v>500</v>
+        <v>52</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -10537,12 +10545,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79993</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10552,7 +10560,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -10560,159 +10568,15 @@
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="n">
-        <v>1000</v>
+        <v>148</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>FBA79439</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>MR-02</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="n">
-        <v>500</v>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>FBA79439</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>MR-02</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>FBA79993</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="n">
-        <v>52</v>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>FBA79993</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>B0GN8WW6BC</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="n">
-        <v>148</v>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
